--- a/docs/design/spotlight/source/回合制作战文档.xlsx
+++ b/docs/design/spotlight/source/回合制作战文档.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20850" windowHeight="10480"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3891,19 +3891,7 @@
               <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
               <a:sym typeface="+mn-ea"/>
             </a:rPr>
-            <a:t>玩家</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1400">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-              <a:sym typeface="+mn-ea"/>
-            </a:rPr>
-            <a:t>被</a:t>
+            <a:t>玩家被</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" altLang="zh-CN" sz="1400">
@@ -7190,10 +7178,10 @@
               <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
               <a:sym typeface="+mn-ea"/>
             </a:rPr>
-            <a:t>4</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1400">
+            <a:t>40%</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
@@ -7202,43 +7190,7 @@
               <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
               <a:sym typeface="+mn-ea"/>
             </a:rPr>
-            <a:t>0%</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1400">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-              <a:sym typeface="+mn-ea"/>
-            </a:rPr>
-            <a:t>概率跳过回合，此时出现屏幕中央闪现提示：怪物处于</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1400">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-              <a:sym typeface="+mn-ea"/>
-            </a:rPr>
-            <a:t>薄醉</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1400">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-              <a:sym typeface="+mn-ea"/>
-            </a:rPr>
-            <a:t>状态，本回合无法行动。</a:t>
+            <a:t>概率跳过回合，此时出现屏幕中央闪现提示：怪物处于薄醉状态，本回合无法行动。</a:t>
           </a:r>
           <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1400">
             <a:solidFill>
@@ -7448,31 +7400,7 @@
               <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
               <a:sym typeface="+mn-ea"/>
             </a:rPr>
-            <a:t>此时出现屏幕中央闪现提示：怪物处于</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1400">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-              <a:sym typeface="+mn-ea"/>
-            </a:rPr>
-            <a:t>醉酒</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1400">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
-              <a:sym typeface="+mn-ea"/>
-            </a:rPr>
-            <a:t>状态，本回合无法行动。</a:t>
+            <a:t>此时出现屏幕中央闪现提示：怪物处于醉酒状态，本回合无法行动。</a:t>
           </a:r>
           <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1400">
             <a:solidFill>
@@ -7525,8 +7453,8 @@
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>244475</xdr:colOff>
-      <xdr:row>187</xdr:row>
-      <xdr:rowOff>178435</xdr:rowOff>
+      <xdr:row>188</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7536,7 +7464,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1838960" y="32867600"/>
-          <a:ext cx="6435725" cy="572135"/>
+          <a:ext cx="6435725" cy="571500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8820,6 +8748,3475 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1959610" y="36442650"/>
+          <a:ext cx="6435725" cy="572135"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>技能施放比例为</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>招式</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>：招式</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>：招式</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>3  =  6</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>3</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>873760</xdr:colOff>
+      <xdr:row>210</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>212</xdr:row>
+      <xdr:rowOff>167005</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1502410" y="37490400"/>
+          <a:ext cx="2365375" cy="382905"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="1" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> 1. </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="1" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>阶段</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="1" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>9BOSS</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400" b="1" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>213</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>197485</xdr:colOff>
+      <xdr:row>216</xdr:row>
+      <xdr:rowOff>13970</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1804670" y="38004750"/>
+          <a:ext cx="2022475" cy="426720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>     BOSS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>机制：</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>215</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>400685</xdr:colOff>
+      <xdr:row>219</xdr:row>
+      <xdr:rowOff>32385</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1995170" y="38411150"/>
+          <a:ext cx="6435725" cy="572135"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>龙族感知敏锐，玩家通过偷袭攻击进入对战的效果和正面战斗进入对战的效果相同</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>238760</xdr:colOff>
+      <xdr:row>225</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>387985</xdr:colOff>
+      <xdr:row>229</xdr:row>
+      <xdr:rowOff>6985</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1982470" y="40163750"/>
+          <a:ext cx="6435725" cy="572135"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>双形态</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:BOSS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>进入战斗时为人形态，在人形态生命值耗尽后为龙形态，两个形态拥有不同的技能组，且在形态切换后，</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>BOSS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>生命值恢复为</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>100%</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>，怒气清空。在第二形态时，</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>BOSS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>在攻击后有</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>20%</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>概率附带一次招式</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>的攻击</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1028700</xdr:colOff>
+      <xdr:row>230</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>50165</xdr:colOff>
+      <xdr:row>233</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1657350" y="41059100"/>
+          <a:ext cx="2022475" cy="426720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>     BOSS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>招式：</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>236</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>327025</xdr:colOff>
+      <xdr:row>248</xdr:row>
+      <xdr:rowOff>132715</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1921510" y="42024300"/>
+          <a:ext cx="6435725" cy="2215515"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>招式</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>：挥动武器，普通攻击，造成一定伤害</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>招式</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>：使用金锁禁锢住玩家，同时造成少量伤害，玩家受到效果</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>“</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>金锁禁锢</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>”</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>，玩家在下</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>个回合只能使用招式</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>攻击（其他招式置暗），且无法使用道具（所有道具置暗）</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>招式</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>3</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>：只能在玩家有</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>“</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>金锁禁锢</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>”</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>效果时使用，引爆印记造成高额伤害，同时增加一次护心麟的效果</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>233</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>235</xdr:row>
+      <xdr:rowOff>165735</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1953260" y="41573450"/>
+          <a:ext cx="1076325" cy="387985"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>人形态：</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>215900</xdr:colOff>
+      <xdr:row>219</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>365125</xdr:colOff>
+      <xdr:row>223</xdr:row>
+      <xdr:rowOff>19685</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1959610" y="39109650"/>
+          <a:ext cx="6435725" cy="572135"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>护心麟</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>:</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>在</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>BOSS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>护心麟状态生效时，可以抵挡一次玩家的任何招式，在人形态护心麟初始为</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>次，转为龙形态后护心麟刷新为</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>次（</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>BOSS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>处于龙形态时，护心麟需要两次攻击才能被击碎）</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>215900</xdr:colOff>
+      <xdr:row>255</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>34925</xdr:colOff>
+      <xdr:row>257</xdr:row>
+      <xdr:rowOff>165735</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1959610" y="45485050"/>
+          <a:ext cx="1076325" cy="387985"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>龙形态：</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>259</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>271</xdr:row>
+      <xdr:rowOff>94615</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1870710" y="46075600"/>
+          <a:ext cx="6435725" cy="2215515"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>招式</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>：挥动武器，普通攻击，造成一定伤害</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>招式</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>BOSS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>进入自我禁锢，在</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>个回合内，</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>BOSS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>的攻击会附带额外伤害，并只能施放招式</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>，在自我禁锢效果结束后，</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>BOSS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>获得护心麟</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>招式</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>3</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>：造成高额伤害，</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>若BOSS拥有护心鳞：消耗掉1次护心鳞，使这次大招伤害提升50%。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>若BOSS没有护心鳞：引爆后，BOSS重新获得1次护心鳞，并回复自身10%的最大生命值。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>249</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>252</xdr:row>
+      <xdr:rowOff>38735</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1965960" y="44284900"/>
+          <a:ext cx="6435725" cy="572135"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>技能施放比例为</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>招式</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>：招式</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2  =  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>5</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>玩家受到招式</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>效果期间施放招式</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>3</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>的概率为三分之一</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>82550</xdr:colOff>
+      <xdr:row>274</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>231775</xdr:colOff>
+      <xdr:row>277</xdr:row>
+      <xdr:rowOff>127635</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1826260" y="48818800"/>
           <a:ext cx="6435725" cy="572135"/>
         </a:xfrm>
         <a:prstGeom prst="rect">

--- a/docs/design/spotlight/source/回合制作战文档.xlsx
+++ b/docs/design/spotlight/source/回合制作战文档.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowWidth="20850" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,12 +32,310 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="97">
   <si>
     <t>聚光灯</t>
   </si>
   <si>
     <t>·</t>
+  </si>
+  <si>
+    <t>属性</t>
+  </si>
+  <si>
+    <t>基础数值</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>最大生命值</t>
+  </si>
+  <si>
+    <t>主角血量，归零战斗失败</t>
+  </si>
+  <si>
+    <t>当前生命值</t>
+  </si>
+  <si>
+    <t>战斗初始</t>
+  </si>
+  <si>
+    <t>基础攻击力</t>
+  </si>
+  <si>
+    <t>所有招式伤害计算基数</t>
+  </si>
+  <si>
+    <t>最大怒气</t>
+  </si>
+  <si>
+    <t>3 点</t>
+  </si>
+  <si>
+    <t>招式消耗上限，怒气不能超过 3</t>
+  </si>
+  <si>
+    <t>初始怒气</t>
+  </si>
+  <si>
+    <t>战斗开局怒气</t>
+  </si>
+  <si>
+    <t>招式</t>
+  </si>
+  <si>
+    <t>消耗怒气</t>
+  </si>
+  <si>
+    <t>伤害效果</t>
+  </si>
+  <si>
+    <t>额外效果</t>
+  </si>
+  <si>
+    <t>招式 1</t>
+  </si>
+  <si>
+    <t>0 怒气</t>
+  </si>
+  <si>
+    <t>100% 基础攻击（18 点）</t>
+  </si>
+  <si>
+    <t>获得 1 点怒气</t>
+  </si>
+  <si>
+    <t>招式 2</t>
+  </si>
+  <si>
+    <t>1 怒气</t>
+  </si>
+  <si>
+    <t>130% 基础攻击（23 点）</t>
+  </si>
+  <si>
+    <t>目标 50% 治疗降低，持续 2 回合</t>
+  </si>
+  <si>
+    <t>招式 3</t>
+  </si>
+  <si>
+    <t>3 怒气</t>
+  </si>
+  <si>
+    <t>180% 基础攻击（32 点）</t>
+  </si>
+  <si>
+    <t>后续 3 次主角攻击 + 8 额外伤害</t>
+  </si>
+  <si>
+    <t>数值</t>
+  </si>
+  <si>
+    <t>战斗血量上限</t>
+  </si>
+  <si>
+    <t>基础攻击</t>
+  </si>
+  <si>
+    <t>所有攻击的伤害基数</t>
+  </si>
+  <si>
+    <t>开局继承醉酒值</t>
+  </si>
+  <si>
+    <t>由进入战斗前决定</t>
+  </si>
+  <si>
+    <t>继承战斗外积累的醉酒值，显示在血条下方</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>消耗 / 触发条件</t>
+  </si>
+  <si>
+    <t>伤害 &amp; 效果数值</t>
+  </si>
+  <si>
+    <t>普通攻击</t>
+  </si>
+  <si>
+    <t>无消耗</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">造成 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>14 点伤害</t>
+    </r>
+  </si>
+  <si>
+    <t>饮酒</t>
+  </si>
+  <si>
+    <t>醉酒值 + 30；回复自身 10% 最大生命 =22点；下一次招式 1 伤害 + 30%（14→18 伤害）</t>
+  </si>
+  <si>
+    <t>狂暴重击</t>
+  </si>
+  <si>
+    <t>1. 正常 / 微醺状态：高额伤害 22 点</t>
+  </si>
+  <si>
+    <t>2. 薄醉状态：22 点伤害 + 眩晕玩家 1 回合</t>
+  </si>
+  <si>
+    <t>人形态血量</t>
+  </si>
+  <si>
+    <t>人形态攻击基数</t>
+  </si>
+  <si>
+    <t>护心麟初始层数</t>
+  </si>
+  <si>
+    <t>抵挡玩家任意 1 次招式伤害</t>
+  </si>
+  <si>
+    <t>触发条件</t>
+  </si>
+  <si>
+    <t>武器挥击</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>16 点伤害</t>
+  </si>
+  <si>
+    <t>金锁禁锢</t>
+  </si>
+  <si>
+    <t>8 点伤害；给玩家附加【金锁禁锢】2 回合：只能使用招式 1，招式 2、3、全部道具禁用</t>
+  </si>
+  <si>
+    <t>印记引爆</t>
+  </si>
+  <si>
+    <t>玩家身上存在金锁禁锢印记</t>
+  </si>
+  <si>
+    <t>26 点高额伤害；BOSS 增加 1 层护心麟</t>
+  </si>
+  <si>
+    <t>切换形态满血重置</t>
+  </si>
+  <si>
+    <t>龙形态攻击基数</t>
+  </si>
+  <si>
+    <t>需要2 次玩家攻击才能击碎</t>
+  </si>
+  <si>
+    <t>平击</t>
+  </si>
+  <si>
+    <t>21 点伤害</t>
+  </si>
+  <si>
+    <t>自我禁锢</t>
+  </si>
+  <si>
+    <t>禁锢自身 2 回合；只能释放招式 1；招式 1 伤害 + 40%；效果结束后获得 1 层护心麟</t>
+  </si>
+  <si>
+    <t>龙威</t>
+  </si>
+  <si>
+    <t>基础伤害32 点</t>
+  </si>
+  <si>
+    <t>有护心麟：消耗护心麟，本次伤害 + 50%（48 伤害）</t>
+  </si>
+  <si>
+    <t>无护心麟：重新获得 1 层护心麟，回复自身 10% 最大生命 =26HP</t>
+  </si>
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>道具名称</t>
+  </si>
+  <si>
+    <t>使用效果</t>
+  </si>
+  <si>
+    <t>活力药剂</t>
+  </si>
+  <si>
+    <t>恢复主角 50 点生命值</t>
+  </si>
+  <si>
+    <t>狂怒结晶</t>
+  </si>
+  <si>
+    <t>主角怒气直接补满至 3 点</t>
+  </si>
+  <si>
+    <t>铁壁护符</t>
+  </si>
+  <si>
+    <t>接下来 2 回合，主角受到全部伤害降低 40%</t>
+  </si>
+  <si>
+    <t>锐锋油膏</t>
+  </si>
+  <si>
+    <t>接下来主角 3 次攻击，基础攻击力 + 7</t>
+  </si>
+  <si>
+    <t>浴血药剂</t>
+  </si>
+  <si>
+    <t>接下来 3 回合，主角每次攻击命中后回复 12 点生命值</t>
+  </si>
+  <si>
+    <t>大瓶生命药剂</t>
+  </si>
+  <si>
+    <t>恢复主角 70 点生命值</t>
+  </si>
+  <si>
+    <t>瞬怒晶石</t>
+  </si>
+  <si>
+    <t>立刻获得 2 点怒气</t>
+  </si>
+  <si>
+    <t>坚韧斗篷</t>
+  </si>
+  <si>
+    <t>生成 1 层护盾，抵挡 1 次任意来源伤害</t>
+  </si>
+  <si>
+    <t>迅击粉末</t>
+  </si>
+  <si>
+    <t>本回合主角可以额外释放一次招式</t>
+  </si>
+  <si>
+    <t>固本甘露</t>
+  </si>
+  <si>
+    <t>接下来 3 回合，回合结束时主角回复 25 点生命值</t>
   </si>
 </sst>
 </file>
@@ -50,7 +348,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -76,6 +374,14 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -458,10 +764,62 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -584,16 +942,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -602,120 +957,123 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -731,6 +1089,33 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="50">
@@ -804,10 +1189,10 @@
       <xdr:rowOff>100330</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>584200</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>147955</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -914,7 +1299,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14311630" y="180975"/>
+          <a:off x="18458180" y="180975"/>
           <a:ext cx="1233170" cy="386080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -983,7 +1368,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="649605" y="931545"/>
+          <a:off x="649605" y="1410970"/>
           <a:ext cx="4306570" cy="354965"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1045,10 +1430,10 @@
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>368300</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>536576</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1057,7 +1442,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2372360" y="0"/>
+          <a:off x="3096260" y="0"/>
           <a:ext cx="11334750" cy="1079500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1128,7 +1513,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="628650" y="901700"/>
+          <a:off x="628650" y="1381125"/>
           <a:ext cx="2876550" cy="325755"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1179,8 +1564,8 @@
       <xdr:rowOff>141605</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>112009</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>277109</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>122555</xdr:rowOff>
     </xdr:to>
@@ -1191,7 +1576,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="885825" y="1576705"/>
+          <a:off x="885825" y="2056130"/>
           <a:ext cx="5370195" cy="336550"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1272,8 +1657,8 @@
       <xdr:rowOff>149860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>138430</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>392430</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>170180</xdr:rowOff>
     </xdr:to>
@@ -1284,7 +1669,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1586865" y="3007360"/>
+          <a:off x="1586865" y="3486785"/>
           <a:ext cx="7210425" cy="553720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1603,13 +1988,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>200660</xdr:colOff>
-      <xdr:row>394</xdr:row>
+      <xdr:row>433</xdr:row>
       <xdr:rowOff>15875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>495935</xdr:colOff>
-      <xdr:row>397</xdr:row>
+      <xdr:row>436</xdr:row>
       <xdr:rowOff>36195</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
@@ -1619,7 +2004,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5087620" y="70081775"/>
+          <a:off x="9234170" y="83746975"/>
           <a:ext cx="7210425" cy="553720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1791,8 +2176,8 @@
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>14605</xdr:rowOff>
     </xdr:to>
@@ -1803,7 +2188,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1369060" y="2489200"/>
+          <a:off x="1369060" y="2968625"/>
           <a:ext cx="2365375" cy="382905"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1979,8 +2364,8 @@
       <xdr:rowOff>173355</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>99060</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3810</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>130810</xdr:rowOff>
     </xdr:to>
@@ -1991,7 +2376,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1350645" y="5342255"/>
+          <a:off x="1350645" y="5821680"/>
           <a:ext cx="1749425" cy="313055"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2167,8 +2552,8 @@
       <xdr:rowOff>13335</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>252095</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>417195</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>172085</xdr:rowOff>
     </xdr:to>
@@ -2179,7 +2564,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1026160" y="7138035"/>
+          <a:off x="1026160" y="7617460"/>
           <a:ext cx="5370195" cy="336550"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2327,8 +2712,8 @@
       <xdr:rowOff>122555</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>382905</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>287655</xdr:colOff>
       <xdr:row>111</xdr:row>
       <xdr:rowOff>149860</xdr:rowOff>
     </xdr:to>
@@ -2339,7 +2724,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1647190" y="19515455"/>
+          <a:off x="1647190" y="19994880"/>
           <a:ext cx="2365375" cy="382905"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2515,8 +2900,8 @@
       <xdr:rowOff>8255</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>193040</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>986790</xdr:colOff>
       <xdr:row>114</xdr:row>
       <xdr:rowOff>174625</xdr:rowOff>
     </xdr:to>
@@ -2527,7 +2912,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1832610" y="20112355"/>
+          <a:off x="1832610" y="20591780"/>
           <a:ext cx="5133340" cy="344170"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2712,8 +3097,8 @@
       <xdr:rowOff>169545</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>316865</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1478915</xdr:colOff>
       <xdr:row>133</xdr:row>
       <xdr:rowOff>12065</xdr:rowOff>
     </xdr:to>
@@ -2724,7 +3109,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1713865" y="23118445"/>
+          <a:off x="1713865" y="23597870"/>
           <a:ext cx="3489960" cy="553720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2879,8 +3264,8 @@
       <xdr:rowOff>69850</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>377825</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>3175</xdr:colOff>
       <xdr:row>245</xdr:row>
       <xdr:rowOff>90170</xdr:rowOff>
     </xdr:to>
@@ -2891,7 +3276,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1826260" y="43110150"/>
+          <a:off x="1826260" y="43589575"/>
           <a:ext cx="7210425" cy="553720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3063,8 +3448,8 @@
       <xdr:rowOff>44450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>536575</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>64770</xdr:rowOff>
     </xdr:to>
@@ -3075,7 +3460,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1356360" y="2012950"/>
+          <a:off x="1356360" y="2492375"/>
           <a:ext cx="7210425" cy="553720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3232,8 +3617,8 @@
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>111125</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>15875</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>141605</xdr:rowOff>
     </xdr:to>
@@ -3244,7 +3629,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1362710" y="3752850"/>
+          <a:off x="1362710" y="4232275"/>
           <a:ext cx="1749425" cy="313055"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3434,8 +3819,8 @@
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>98425</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
@@ -3446,7 +3831,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1546860" y="4267200"/>
+          <a:off x="1546860" y="4746625"/>
           <a:ext cx="7210425" cy="553720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3733,8 +4118,8 @@
       <xdr:rowOff>156210</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>63500</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>317500</xdr:colOff>
       <xdr:row>35</xdr:row>
       <xdr:rowOff>176530</xdr:rowOff>
     </xdr:to>
@@ -3745,7 +4130,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1511935" y="5858510"/>
+          <a:off x="1511935" y="6337935"/>
           <a:ext cx="7210425" cy="553720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4068,8 +4453,8 @@
       <xdr:rowOff>62230</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>149860</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>403860</xdr:colOff>
       <xdr:row>71</xdr:row>
       <xdr:rowOff>107950</xdr:rowOff>
     </xdr:to>
@@ -4088,7 +4473,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="857250" y="9142730"/>
+          <a:off x="857250" y="9622155"/>
           <a:ext cx="7951470" cy="3601720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4110,8 +4495,8 @@
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>456565</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>81915</xdr:colOff>
       <xdr:row>47</xdr:row>
       <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
@@ -4122,7 +4507,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1276350" y="7899400"/>
+          <a:off x="1276350" y="8378825"/>
           <a:ext cx="7210425" cy="553720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4334,8 +4719,8 @@
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>329565</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>234315</xdr:colOff>
       <xdr:row>49</xdr:row>
       <xdr:rowOff>116205</xdr:rowOff>
     </xdr:to>
@@ -4346,7 +4731,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1593850" y="8458200"/>
+          <a:off x="1593850" y="8937625"/>
           <a:ext cx="2365375" cy="382905"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4522,8 +4907,8 @@
       <xdr:rowOff>60325</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>436245</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>61595</xdr:colOff>
       <xdr:row>103</xdr:row>
       <xdr:rowOff>80645</xdr:rowOff>
     </xdr:to>
@@ -4534,7 +4919,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1884680" y="17853025"/>
+          <a:off x="1884680" y="18332450"/>
           <a:ext cx="7210425" cy="553720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4896,8 +5281,8 @@
       <xdr:rowOff>8255</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>225425</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2276475</xdr:colOff>
       <xdr:row>119</xdr:row>
       <xdr:rowOff>46990</xdr:rowOff>
     </xdr:to>
@@ -4908,7 +5293,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1819910" y="20645755"/>
+          <a:off x="1819910" y="21125180"/>
           <a:ext cx="6435725" cy="572135"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5165,8 +5550,8 @@
       <xdr:rowOff>103505</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>174625</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2225675</xdr:colOff>
       <xdr:row>123</xdr:row>
       <xdr:rowOff>142240</xdr:rowOff>
     </xdr:to>
@@ -5177,7 +5562,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1769110" y="21452205"/>
+          <a:off x="1769110" y="21931630"/>
           <a:ext cx="6435725" cy="572135"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5446,8 +5831,8 @@
       <xdr:rowOff>14605</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>145415</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2196465</xdr:colOff>
       <xdr:row>128</xdr:row>
       <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
@@ -5458,7 +5843,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1739900" y="22252305"/>
+          <a:off x="1739900" y="22731730"/>
           <a:ext cx="6435725" cy="572135"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5715,8 +6100,8 @@
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>295910</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1457960</xdr:colOff>
       <xdr:row>136</xdr:row>
       <xdr:rowOff>58420</xdr:rowOff>
     </xdr:to>
@@ -5727,7 +6112,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1692910" y="23698200"/>
+          <a:off x="1692910" y="24177625"/>
           <a:ext cx="3489960" cy="553720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5882,8 +6267,8 @@
       <xdr:rowOff>41910</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>340995</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>506095</xdr:colOff>
       <xdr:row>141</xdr:row>
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:to>
@@ -5894,7 +6279,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1115060" y="24768810"/>
+          <a:off x="1115060" y="25248235"/>
           <a:ext cx="5370195" cy="336550"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6072,8 +6457,8 @@
       <xdr:rowOff>146685</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>260985</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>165735</xdr:colOff>
       <xdr:row>145</xdr:row>
       <xdr:rowOff>173990</xdr:rowOff>
     </xdr:to>
@@ -6084,7 +6469,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1525270" y="25584785"/>
+          <a:off x="1525270" y="26064210"/>
           <a:ext cx="2365375" cy="382905"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6274,8 +6659,8 @@
       <xdr:rowOff>167005</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>493395</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>118745</xdr:colOff>
       <xdr:row>98</xdr:row>
       <xdr:rowOff>64135</xdr:rowOff>
     </xdr:to>
@@ -6294,7 +6679,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1709420" y="13870305"/>
+          <a:off x="1709420" y="14349730"/>
           <a:ext cx="6814185" cy="3630930"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6316,8 +6701,8 @@
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>92710</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2143760</xdr:colOff>
       <xdr:row>152</xdr:row>
       <xdr:rowOff>162560</xdr:rowOff>
     </xdr:to>
@@ -6328,7 +6713,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1687195" y="26628725"/>
+          <a:off x="1687195" y="27108150"/>
           <a:ext cx="6435725" cy="572135"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6486,8 +6871,8 @@
       <xdr:rowOff>132715</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>86360</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2137410</xdr:colOff>
       <xdr:row>153</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
@@ -6498,7 +6883,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1680845" y="26815415"/>
+          <a:off x="1680845" y="27294840"/>
           <a:ext cx="6435725" cy="572135"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6644,8 +7029,8 @@
       <xdr:rowOff>56515</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>212725</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1374775</xdr:colOff>
       <xdr:row>167</xdr:row>
       <xdr:rowOff>37465</xdr:rowOff>
     </xdr:to>
@@ -6664,7 +7049,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2146935" y="27628215"/>
+          <a:off x="2146935" y="28107640"/>
           <a:ext cx="2952750" cy="2114550"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6686,8 +7071,8 @@
       <xdr:rowOff>82550</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>136525</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
       <xdr:row>178</xdr:row>
       <xdr:rowOff>139065</xdr:rowOff>
     </xdr:to>
@@ -6698,7 +7083,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1826260" y="29965650"/>
+          <a:off x="1826260" y="30445075"/>
           <a:ext cx="8226425" cy="1834515"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7451,8 +7836,8 @@
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>244475</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2295525</xdr:colOff>
       <xdr:row>188</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -7463,7 +7848,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1838960" y="32867600"/>
+          <a:off x="1838960" y="33347025"/>
           <a:ext cx="6435725" cy="571500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7621,8 +8006,8 @@
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>149225</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>53975</xdr:colOff>
       <xdr:row>193</xdr:row>
       <xdr:rowOff>134620</xdr:rowOff>
     </xdr:to>
@@ -7633,7 +8018,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1756410" y="34036000"/>
+          <a:off x="1756410" y="34515425"/>
           <a:ext cx="2022475" cy="426720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7791,8 +8176,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>136525</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>41275</xdr:colOff>
       <xdr:row>149</xdr:row>
       <xdr:rowOff>71120</xdr:rowOff>
     </xdr:to>
@@ -7803,7 +8188,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1743710" y="26149300"/>
+          <a:off x="1743710" y="26628725"/>
           <a:ext cx="2022475" cy="426720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7961,8 +8346,8 @@
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>225425</xdr:colOff>
       <xdr:row>205</xdr:row>
       <xdr:rowOff>12065</xdr:rowOff>
     </xdr:to>
@@ -7973,7 +8358,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1661160" y="34639250"/>
+          <a:off x="1661160" y="35118675"/>
           <a:ext cx="8226425" cy="1834515"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -8144,8 +8529,8 @@
       <xdr:rowOff>146050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>250825</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2301875</xdr:colOff>
       <xdr:row>201</xdr:row>
       <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
@@ -8156,7 +8541,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1845310" y="34474150"/>
+          <a:off x="1845310" y="34953575"/>
           <a:ext cx="6435725" cy="1377950"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -8735,8 +9120,8 @@
       <xdr:rowOff>158750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>365125</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2416175</xdr:colOff>
       <xdr:row>208</xdr:row>
       <xdr:rowOff>19685</xdr:rowOff>
     </xdr:to>
@@ -8747,7 +9132,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1959610" y="36442650"/>
+          <a:off x="1959610" y="36922075"/>
           <a:ext cx="6435725" cy="572135"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -9037,8 +9422,8 @@
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
       <xdr:row>212</xdr:row>
       <xdr:rowOff>167005</xdr:rowOff>
     </xdr:to>
@@ -9049,7 +9434,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1502410" y="37490400"/>
+          <a:off x="1502410" y="37969825"/>
           <a:ext cx="2365375" cy="382905"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -9239,8 +9624,8 @@
       <xdr:rowOff>120650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>197485</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>102235</xdr:colOff>
       <xdr:row>216</xdr:row>
       <xdr:rowOff>13970</xdr:rowOff>
     </xdr:to>
@@ -9251,7 +9636,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1804670" y="38004750"/>
+          <a:off x="1804670" y="38484175"/>
           <a:ext cx="2022475" cy="426720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -9409,8 +9794,8 @@
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>400685</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>26035</xdr:colOff>
       <xdr:row>219</xdr:row>
       <xdr:rowOff>32385</xdr:rowOff>
     </xdr:to>
@@ -9421,7 +9806,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1995170" y="38411150"/>
+          <a:off x="1995170" y="38890575"/>
           <a:ext cx="6435725" cy="572135"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -9579,8 +9964,8 @@
       <xdr:rowOff>146050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>387985</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>13335</xdr:colOff>
       <xdr:row>229</xdr:row>
       <xdr:rowOff>6985</xdr:rowOff>
     </xdr:to>
@@ -9591,7 +9976,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1982470" y="40163750"/>
+          <a:off x="1982470" y="40643175"/>
           <a:ext cx="6435725" cy="572135"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -9893,8 +10278,8 @@
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>50165</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>583565</xdr:colOff>
       <xdr:row>233</xdr:row>
       <xdr:rowOff>45720</xdr:rowOff>
     </xdr:to>
@@ -9905,7 +10290,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1657350" y="41059100"/>
+          <a:off x="1657350" y="41538525"/>
           <a:ext cx="2022475" cy="426720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -10063,8 +10448,8 @@
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>327025</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2378075</xdr:colOff>
       <xdr:row>248</xdr:row>
       <xdr:rowOff>132715</xdr:rowOff>
     </xdr:to>
@@ -10075,7 +10460,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1921510" y="42024300"/>
+          <a:off x="1921510" y="42503725"/>
           <a:ext cx="6435725" cy="2215515"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -10615,8 +11000,8 @@
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1285875</xdr:colOff>
       <xdr:row>235</xdr:row>
       <xdr:rowOff>165735</xdr:rowOff>
     </xdr:to>
@@ -10627,7 +11012,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1953260" y="41573450"/>
+          <a:off x="1953260" y="42052875"/>
           <a:ext cx="1076325" cy="387985"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -10785,8 +11170,8 @@
       <xdr:rowOff>158750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>365125</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2416175</xdr:colOff>
       <xdr:row>223</xdr:row>
       <xdr:rowOff>19685</xdr:rowOff>
     </xdr:to>
@@ -10797,7 +11182,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1959610" y="39109650"/>
+          <a:off x="1959610" y="39589075"/>
           <a:ext cx="6435725" cy="572135"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -11075,8 +11460,8 @@
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>34925</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1292225</xdr:colOff>
       <xdr:row>257</xdr:row>
       <xdr:rowOff>165735</xdr:rowOff>
     </xdr:to>
@@ -11087,7 +11472,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1959610" y="45485050"/>
+          <a:off x="1959610" y="45964475"/>
           <a:ext cx="1076325" cy="387985"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -11245,8 +11630,8 @@
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2327275</xdr:colOff>
       <xdr:row>271</xdr:row>
       <xdr:rowOff>94615</xdr:rowOff>
     </xdr:to>
@@ -11257,7 +11642,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1870710" y="46075600"/>
+          <a:off x="1870710" y="46555025"/>
           <a:ext cx="6435725" cy="2215515"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -11851,8 +12236,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>371475</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2422525</xdr:colOff>
       <xdr:row>252</xdr:row>
       <xdr:rowOff>38735</xdr:rowOff>
     </xdr:to>
@@ -11863,7 +12248,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1965960" y="44284900"/>
+          <a:off x="1965960" y="44764325"/>
           <a:ext cx="6435725" cy="572135"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -12204,8 +12589,8 @@
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>231775</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2282825</xdr:colOff>
       <xdr:row>277</xdr:row>
       <xdr:rowOff>127635</xdr:rowOff>
     </xdr:to>
@@ -12216,7 +12601,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1826260" y="48818800"/>
+          <a:off x="1826260" y="49298225"/>
           <a:ext cx="6435725" cy="572135"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -12492,6 +12877,2306 @@
             <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
             <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
             <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>683260</xdr:colOff>
+      <xdr:row>282</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>702945</xdr:colOff>
+      <xdr:row>284</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1311910" y="50650775"/>
+          <a:ext cx="5370195" cy="336550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="2000" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="12"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>四、数值相关</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1050" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="12"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>286</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>288</xdr:row>
+      <xdr:rowOff>109855</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1750060" y="51425475"/>
+          <a:ext cx="2365375" cy="382905"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="1" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> 1. </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="1" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>主角数值</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400" b="1" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>289</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>178435</xdr:colOff>
+      <xdr:row>291</xdr:row>
+      <xdr:rowOff>109220</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1880870" y="51914425"/>
+          <a:ext cx="2022475" cy="426720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>基础数值：</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>301</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>178435</xdr:colOff>
+      <xdr:row>304</xdr:row>
+      <xdr:rowOff>26670</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1880870" y="55810150"/>
+          <a:ext cx="2022475" cy="426720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>招式数值：</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>92710</xdr:colOff>
+      <xdr:row>315</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>476885</xdr:colOff>
+      <xdr:row>317</xdr:row>
+      <xdr:rowOff>160655</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1836420" y="59413775"/>
+          <a:ext cx="2365375" cy="382905"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="1" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> 2. </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="1" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>阶段</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="1" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1 BOSS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="1" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>数值</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400" b="1" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>340360</xdr:colOff>
+      <xdr:row>319</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>381635</xdr:colOff>
+      <xdr:row>321</xdr:row>
+      <xdr:rowOff>90170</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2084070" y="60010675"/>
+          <a:ext cx="2022475" cy="426720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>基础数值：</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>397510</xdr:colOff>
+      <xdr:row>331</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>438785</xdr:colOff>
+      <xdr:row>333</xdr:row>
+      <xdr:rowOff>153670</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2141220" y="62433200"/>
+          <a:ext cx="2022475" cy="426720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>招式数值：</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>181610</xdr:colOff>
+      <xdr:row>345</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>565785</xdr:colOff>
+      <xdr:row>347</xdr:row>
+      <xdr:rowOff>109855</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1925320" y="65512950"/>
+          <a:ext cx="2365375" cy="382905"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>   </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="1" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> 3. </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="1" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>阶段</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="1" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>9 BOSS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="1" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>数值</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400" b="1" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>422910</xdr:colOff>
+      <xdr:row>348</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>464185</xdr:colOff>
+      <xdr:row>350</xdr:row>
+      <xdr:rowOff>172720</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2166620" y="66065400"/>
+          <a:ext cx="2022475" cy="426720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>人形态基础数值：</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>346710</xdr:colOff>
+      <xdr:row>359</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>387985</xdr:colOff>
+      <xdr:row>361</xdr:row>
+      <xdr:rowOff>128270</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2090420" y="68024375"/>
+          <a:ext cx="2022475" cy="426720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>人形态招式数值：</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>372110</xdr:colOff>
+      <xdr:row>371</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>413385</xdr:colOff>
+      <xdr:row>373</xdr:row>
+      <xdr:rowOff>134620</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2115820" y="70745350"/>
+          <a:ext cx="2022475" cy="426720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>龙形态基础数值：</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>308610</xdr:colOff>
+      <xdr:row>382</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>349885</xdr:colOff>
+      <xdr:row>385</xdr:row>
+      <xdr:rowOff>20320</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2052320" y="72812275"/>
+          <a:ext cx="2022475" cy="426720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>     </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>龙形态招式数值：</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1400" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>930910</xdr:colOff>
+      <xdr:row>397</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>950595</xdr:colOff>
+      <xdr:row>399</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="文本框架 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1559560" y="76238100"/>
+          <a:ext cx="5370195" cy="336550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN"/>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="2000" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="12"/>
+              <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>五、道具相关</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1050" b="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:uFillTx/>
+            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="12"/>
+            <a:ea typeface="微软雅黑" panose="020B0503020204020204" charset="-122"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -12751,10 +15436,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AO400"/>
+  <dimension ref="A1:AO439"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="15.9636363636364" customWidth="1"/>
+    <col min="3" max="3" width="19.3636363636364" customWidth="1"/>
+    <col min="5" max="5" width="32.2727272727273" customWidth="1"/>
+    <col min="6" max="6" width="34.7272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1" spans="1:41">
@@ -12888,7 +15576,7 @@
       <c r="AN3" s="2"/>
       <c r="AO3" s="2"/>
     </row>
-    <row r="4" ht="14.25" customHeight="1" spans="1:41">
+    <row r="4" ht="52" customHeight="1" spans="1:41">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="2"/>
@@ -25317,7 +28005,7 @@
       <c r="AN292" s="3"/>
       <c r="AO292" s="3"/>
     </row>
-    <row r="293" spans="1:41">
+    <row r="293" ht="14.75" spans="1:41">
       <c r="A293" s="3"/>
       <c r="B293" s="3"/>
       <c r="C293" s="3"/>
@@ -25360,12 +28048,18 @@
       <c r="AN293" s="3"/>
       <c r="AO293" s="3"/>
     </row>
-    <row r="294" spans="1:41">
+    <row r="294" ht="14.75" spans="1:41">
       <c r="A294" s="3"/>
       <c r="B294" s="3"/>
-      <c r="C294" s="3"/>
-      <c r="D294" s="3"/>
-      <c r="E294" s="3"/>
+      <c r="C294" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D294" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E294" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="F294" s="3"/>
       <c r="G294" s="3"/>
       <c r="H294" s="3"/>
@@ -25403,12 +28097,18 @@
       <c r="AN294" s="3"/>
       <c r="AO294" s="3"/>
     </row>
-    <row r="295" spans="1:41">
+    <row r="295" ht="42.75" spans="1:41">
       <c r="A295" s="3"/>
       <c r="B295" s="3"/>
-      <c r="C295" s="3"/>
-      <c r="D295" s="3"/>
-      <c r="E295" s="3"/>
+      <c r="C295" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D295" s="10">
+        <v>120</v>
+      </c>
+      <c r="E295" s="10" t="s">
+        <v>6</v>
+      </c>
       <c r="F295" s="3"/>
       <c r="G295" s="3"/>
       <c r="H295" s="3"/>
@@ -25446,12 +28146,18 @@
       <c r="AN295" s="3"/>
       <c r="AO295" s="3"/>
     </row>
-    <row r="296" spans="1:41">
+    <row r="296" ht="28.75" spans="1:41">
       <c r="A296" s="3"/>
       <c r="B296" s="3"/>
-      <c r="C296" s="3"/>
-      <c r="D296" s="3"/>
-      <c r="E296" s="3"/>
+      <c r="C296" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D296" s="10">
+        <v>120</v>
+      </c>
+      <c r="E296" s="10" t="s">
+        <v>8</v>
+      </c>
       <c r="F296" s="3"/>
       <c r="G296" s="3"/>
       <c r="H296" s="3"/>
@@ -25489,12 +28195,18 @@
       <c r="AN296" s="3"/>
       <c r="AO296" s="3"/>
     </row>
-    <row r="297" spans="1:41">
+    <row r="297" ht="42.75" spans="1:41">
       <c r="A297" s="3"/>
       <c r="B297" s="3"/>
-      <c r="C297" s="3"/>
-      <c r="D297" s="3"/>
-      <c r="E297" s="3"/>
+      <c r="C297" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D297" s="10">
+        <v>18</v>
+      </c>
+      <c r="E297" s="10" t="s">
+        <v>10</v>
+      </c>
       <c r="F297" s="3"/>
       <c r="G297" s="3"/>
       <c r="H297" s="3"/>
@@ -25532,12 +28244,18 @@
       <c r="AN297" s="3"/>
       <c r="AO297" s="3"/>
     </row>
-    <row r="298" spans="1:41">
+    <row r="298" ht="56.75" spans="1:41">
       <c r="A298" s="3"/>
       <c r="B298" s="3"/>
-      <c r="C298" s="3"/>
-      <c r="D298" s="3"/>
-      <c r="E298" s="3"/>
+      <c r="C298" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D298" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E298" s="10" t="s">
+        <v>13</v>
+      </c>
       <c r="F298" s="3"/>
       <c r="G298" s="3"/>
       <c r="H298" s="3"/>
@@ -25575,12 +28293,18 @@
       <c r="AN298" s="3"/>
       <c r="AO298" s="3"/>
     </row>
-    <row r="299" spans="1:41">
+    <row r="299" ht="28.75" spans="1:41">
       <c r="A299" s="3"/>
       <c r="B299" s="3"/>
-      <c r="C299" s="3"/>
-      <c r="D299" s="3"/>
-      <c r="E299" s="3"/>
+      <c r="C299" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D299" s="10">
+        <v>0</v>
+      </c>
+      <c r="E299" s="10" t="s">
+        <v>15</v>
+      </c>
       <c r="F299" s="3"/>
       <c r="G299" s="3"/>
       <c r="H299" s="3"/>
@@ -25876,7 +28600,7 @@
       <c r="AN305" s="3"/>
       <c r="AO305" s="3"/>
     </row>
-    <row r="306" spans="1:41">
+    <row r="306" ht="14.75" spans="1:41">
       <c r="A306" s="3"/>
       <c r="B306" s="3"/>
       <c r="C306" s="3"/>
@@ -25919,13 +28643,21 @@
       <c r="AN306" s="3"/>
       <c r="AO306" s="3"/>
     </row>
-    <row r="307" spans="1:41">
+    <row r="307" ht="14.75" spans="1:41">
       <c r="A307" s="3"/>
       <c r="B307" s="3"/>
-      <c r="C307" s="3"/>
-      <c r="D307" s="3"/>
-      <c r="E307" s="3"/>
-      <c r="F307" s="3"/>
+      <c r="C307" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D307" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E307" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F307" s="9" t="s">
+        <v>19</v>
+      </c>
       <c r="G307" s="3"/>
       <c r="H307" s="3"/>
       <c r="I307" s="3"/>
@@ -25962,13 +28694,21 @@
       <c r="AN307" s="3"/>
       <c r="AO307" s="3"/>
     </row>
-    <row r="308" spans="1:41">
+    <row r="308" ht="14.75" spans="1:41">
       <c r="A308" s="3"/>
       <c r="B308" s="3"/>
-      <c r="C308" s="3"/>
-      <c r="D308" s="3"/>
-      <c r="E308" s="3"/>
-      <c r="F308" s="3"/>
+      <c r="C308" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D308" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E308" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F308" s="10" t="s">
+        <v>23</v>
+      </c>
       <c r="G308" s="3"/>
       <c r="H308" s="3"/>
       <c r="I308" s="3"/>
@@ -26005,13 +28745,21 @@
       <c r="AN308" s="3"/>
       <c r="AO308" s="3"/>
     </row>
-    <row r="309" spans="1:41">
+    <row r="309" ht="56.75" spans="1:41">
       <c r="A309" s="3"/>
       <c r="B309" s="3"/>
-      <c r="C309" s="3"/>
-      <c r="D309" s="3"/>
-      <c r="E309" s="3"/>
-      <c r="F309" s="3"/>
+      <c r="C309" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D309" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E309" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F309" s="10" t="s">
+        <v>27</v>
+      </c>
       <c r="G309" s="3"/>
       <c r="H309" s="3"/>
       <c r="I309" s="3"/>
@@ -26048,13 +28796,21 @@
       <c r="AN309" s="3"/>
       <c r="AO309" s="3"/>
     </row>
-    <row r="310" spans="1:41">
+    <row r="310" ht="56.75" spans="1:41">
       <c r="A310" s="3"/>
       <c r="B310" s="3"/>
-      <c r="C310" s="3"/>
-      <c r="D310" s="3"/>
-      <c r="E310" s="3"/>
-      <c r="F310" s="3"/>
+      <c r="C310" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D310" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E310" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F310" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="G310" s="3"/>
       <c r="H310" s="3"/>
       <c r="I310" s="3"/>
@@ -26564,7 +29320,7 @@
       <c r="AN321" s="3"/>
       <c r="AO321" s="3"/>
     </row>
-    <row r="322" spans="1:41">
+    <row r="322" ht="14.75" spans="1:41">
       <c r="A322" s="3"/>
       <c r="B322" s="3"/>
       <c r="C322" s="3"/>
@@ -26607,12 +29363,18 @@
       <c r="AN322" s="3"/>
       <c r="AO322" s="3"/>
     </row>
-    <row r="323" spans="1:41">
+    <row r="323" ht="14.75" spans="1:41">
       <c r="A323" s="3"/>
       <c r="B323" s="3"/>
-      <c r="C323" s="3"/>
-      <c r="D323" s="3"/>
-      <c r="E323" s="3"/>
+      <c r="C323" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D323" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E323" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="F323" s="3"/>
       <c r="G323" s="3"/>
       <c r="H323" s="3"/>
@@ -26650,12 +29412,18 @@
       <c r="AN323" s="3"/>
       <c r="AO323" s="3"/>
     </row>
-    <row r="324" spans="1:41">
+    <row r="324" ht="14.75" spans="1:41">
       <c r="A324" s="3"/>
       <c r="B324" s="3"/>
-      <c r="C324" s="3"/>
-      <c r="D324" s="3"/>
-      <c r="E324" s="3"/>
+      <c r="C324" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D324" s="10">
+        <v>220</v>
+      </c>
+      <c r="E324" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="F324" s="3"/>
       <c r="G324" s="3"/>
       <c r="H324" s="3"/>
@@ -26693,12 +29461,18 @@
       <c r="AN324" s="3"/>
       <c r="AO324" s="3"/>
     </row>
-    <row r="325" spans="1:41">
+    <row r="325" ht="14.75" spans="1:41">
       <c r="A325" s="3"/>
       <c r="B325" s="3"/>
-      <c r="C325" s="3"/>
-      <c r="D325" s="3"/>
-      <c r="E325" s="3"/>
+      <c r="C325" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D325" s="10">
+        <v>14</v>
+      </c>
+      <c r="E325" s="10" t="s">
+        <v>35</v>
+      </c>
       <c r="F325" s="3"/>
       <c r="G325" s="3"/>
       <c r="H325" s="3"/>
@@ -26736,12 +29510,18 @@
       <c r="AN325" s="3"/>
       <c r="AO325" s="3"/>
     </row>
-    <row r="326" spans="1:41">
+    <row r="326" ht="28.75" spans="1:41">
       <c r="A326" s="3"/>
       <c r="B326" s="3"/>
-      <c r="C326" s="3"/>
-      <c r="D326" s="3"/>
-      <c r="E326" s="3"/>
+      <c r="C326" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D326" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E326" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="F326" s="3"/>
       <c r="G326" s="3"/>
       <c r="H326" s="3"/>
@@ -27123,7 +29903,7 @@
       <c r="AN334" s="3"/>
       <c r="AO334" s="3"/>
     </row>
-    <row r="335" spans="1:41">
+    <row r="335" ht="14.75" spans="1:41">
       <c r="A335" s="3"/>
       <c r="B335" s="3"/>
       <c r="C335" s="3"/>
@@ -27166,13 +29946,21 @@
       <c r="AN335" s="3"/>
       <c r="AO335" s="3"/>
     </row>
-    <row r="336" spans="1:41">
+    <row r="336" ht="14.75" spans="1:41">
       <c r="A336" s="3"/>
       <c r="B336" s="3"/>
-      <c r="C336" s="3"/>
-      <c r="D336" s="3"/>
-      <c r="E336" s="3"/>
-      <c r="F336" s="3"/>
+      <c r="C336" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D336" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E336" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F336" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="G336" s="3"/>
       <c r="H336" s="3"/>
       <c r="I336" s="3"/>
@@ -27209,13 +29997,21 @@
       <c r="AN336" s="3"/>
       <c r="AO336" s="3"/>
     </row>
-    <row r="337" spans="1:41">
+    <row r="337" ht="14.75" spans="1:41">
       <c r="A337" s="3"/>
       <c r="B337" s="3"/>
-      <c r="C337" s="3"/>
-      <c r="D337" s="3"/>
-      <c r="E337" s="3"/>
-      <c r="F337" s="3"/>
+      <c r="C337" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D337" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E337" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F337" s="10" t="s">
+        <v>44</v>
+      </c>
       <c r="G337" s="3"/>
       <c r="H337" s="3"/>
       <c r="I337" s="3"/>
@@ -27252,13 +30048,21 @@
       <c r="AN337" s="3"/>
       <c r="AO337" s="3"/>
     </row>
-    <row r="338" spans="1:41">
+    <row r="338" ht="42.75" spans="1:41">
       <c r="A338" s="3"/>
       <c r="B338" s="3"/>
-      <c r="C338" s="3"/>
-      <c r="D338" s="3"/>
-      <c r="E338" s="3"/>
-      <c r="F338" s="3"/>
+      <c r="C338" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D338" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E338" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F338" s="11" t="s">
+        <v>46</v>
+      </c>
       <c r="G338" s="3"/>
       <c r="H338" s="3"/>
       <c r="I338" s="3"/>
@@ -27295,13 +30099,21 @@
       <c r="AN338" s="3"/>
       <c r="AO338" s="3"/>
     </row>
-    <row r="339" spans="1:41">
+    <row r="339" ht="14.75" spans="1:41">
       <c r="A339" s="3"/>
       <c r="B339" s="3"/>
-      <c r="C339" s="3"/>
-      <c r="D339" s="3"/>
-      <c r="E339" s="3"/>
-      <c r="F339" s="3"/>
+      <c r="C339" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D339" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E339" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F339" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="G339" s="3"/>
       <c r="H339" s="3"/>
       <c r="I339" s="3"/>
@@ -27338,13 +30150,15 @@
       <c r="AN339" s="3"/>
       <c r="AO339" s="3"/>
     </row>
-    <row r="340" spans="1:41">
+    <row r="340" ht="28.75" spans="1:41">
       <c r="A340" s="3"/>
       <c r="B340" s="3"/>
-      <c r="C340" s="3"/>
-      <c r="D340" s="3"/>
-      <c r="E340" s="3"/>
-      <c r="F340" s="3"/>
+      <c r="C340" s="10"/>
+      <c r="D340" s="10"/>
+      <c r="E340" s="10"/>
+      <c r="F340" s="13" t="s">
+        <v>49</v>
+      </c>
       <c r="G340" s="3"/>
       <c r="H340" s="3"/>
       <c r="I340" s="3"/>
@@ -27854,7 +30668,7 @@
       <c r="AN351" s="3"/>
       <c r="AO351" s="3"/>
     </row>
-    <row r="352" spans="1:41">
+    <row r="352" ht="14.75" spans="1:41">
       <c r="A352" s="3"/>
       <c r="B352" s="3"/>
       <c r="C352" s="3"/>
@@ -27897,12 +30711,18 @@
       <c r="AN352" s="3"/>
       <c r="AO352" s="3"/>
     </row>
-    <row r="353" spans="1:41">
+    <row r="353" ht="14.75" spans="1:41">
       <c r="A353" s="3"/>
       <c r="B353" s="3"/>
-      <c r="C353" s="3"/>
-      <c r="D353" s="3"/>
-      <c r="E353" s="3"/>
+      <c r="C353" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D353" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E353" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="F353" s="3"/>
       <c r="G353" s="3"/>
       <c r="H353" s="3"/>
@@ -27940,12 +30760,18 @@
       <c r="AN353" s="3"/>
       <c r="AO353" s="3"/>
     </row>
-    <row r="354" spans="1:41">
+    <row r="354" ht="14.75" spans="1:41">
       <c r="A354" s="3"/>
       <c r="B354" s="3"/>
-      <c r="C354" s="3"/>
-      <c r="D354" s="3"/>
-      <c r="E354" s="3"/>
+      <c r="C354" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D354" s="10">
+        <v>260</v>
+      </c>
+      <c r="E354" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="F354" s="3"/>
       <c r="G354" s="3"/>
       <c r="H354" s="3"/>
@@ -27983,12 +30809,18 @@
       <c r="AN354" s="3"/>
       <c r="AO354" s="3"/>
     </row>
-    <row r="355" spans="1:41">
+    <row r="355" ht="14.75" spans="1:41">
       <c r="A355" s="3"/>
       <c r="B355" s="3"/>
-      <c r="C355" s="3"/>
-      <c r="D355" s="3"/>
-      <c r="E355" s="3"/>
+      <c r="C355" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D355" s="10">
+        <v>16</v>
+      </c>
+      <c r="E355" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="F355" s="3"/>
       <c r="G355" s="3"/>
       <c r="H355" s="3"/>
@@ -28026,12 +30858,18 @@
       <c r="AN355" s="3"/>
       <c r="AO355" s="3"/>
     </row>
-    <row r="356" spans="1:41">
+    <row r="356" ht="14.75" spans="1:41">
       <c r="A356" s="3"/>
       <c r="B356" s="3"/>
-      <c r="C356" s="3"/>
-      <c r="D356" s="3"/>
-      <c r="E356" s="3"/>
+      <c r="C356" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D356" s="10">
+        <v>1</v>
+      </c>
+      <c r="E356" s="10" t="s">
+        <v>53</v>
+      </c>
       <c r="F356" s="3"/>
       <c r="G356" s="3"/>
       <c r="H356" s="3"/>
@@ -28327,7 +31165,7 @@
       <c r="AN362" s="3"/>
       <c r="AO362" s="3"/>
     </row>
-    <row r="363" spans="1:41">
+    <row r="363" ht="14.75" spans="1:41">
       <c r="A363" s="3"/>
       <c r="B363" s="3"/>
       <c r="C363" s="3"/>
@@ -28370,13 +31208,21 @@
       <c r="AN363" s="3"/>
       <c r="AO363" s="3"/>
     </row>
-    <row r="364" spans="1:41">
+    <row r="364" ht="14.75" spans="1:41">
       <c r="A364" s="3"/>
       <c r="B364" s="3"/>
-      <c r="C364" s="3"/>
-      <c r="D364" s="3"/>
-      <c r="E364" s="3"/>
-      <c r="F364" s="3"/>
+      <c r="C364" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D364" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E364" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F364" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="G364" s="3"/>
       <c r="H364" s="3"/>
       <c r="I364" s="3"/>
@@ -28413,13 +31259,21 @@
       <c r="AN364" s="3"/>
       <c r="AO364" s="3"/>
     </row>
-    <row r="365" spans="1:41">
+    <row r="365" ht="14.75" spans="1:41">
       <c r="A365" s="3"/>
       <c r="B365" s="3"/>
-      <c r="C365" s="3"/>
-      <c r="D365" s="3"/>
-      <c r="E365" s="3"/>
-      <c r="F365" s="3"/>
+      <c r="C365" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D365" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E365" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F365" s="11" t="s">
+        <v>57</v>
+      </c>
       <c r="G365" s="3"/>
       <c r="H365" s="3"/>
       <c r="I365" s="3"/>
@@ -28456,13 +31310,21 @@
       <c r="AN365" s="3"/>
       <c r="AO365" s="3"/>
     </row>
-    <row r="366" spans="1:41">
+    <row r="366" ht="42.75" spans="1:41">
       <c r="A366" s="3"/>
       <c r="B366" s="3"/>
-      <c r="C366" s="3"/>
-      <c r="D366" s="3"/>
-      <c r="E366" s="3"/>
-      <c r="F366" s="3"/>
+      <c r="C366" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D366" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E366" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F366" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="G366" s="3"/>
       <c r="H366" s="3"/>
       <c r="I366" s="3"/>
@@ -28499,13 +31361,21 @@
       <c r="AN366" s="3"/>
       <c r="AO366" s="3"/>
     </row>
-    <row r="367" spans="1:41">
+    <row r="367" ht="28.75" spans="1:41">
       <c r="A367" s="3"/>
       <c r="B367" s="3"/>
-      <c r="C367" s="3"/>
-      <c r="D367" s="3"/>
-      <c r="E367" s="3"/>
-      <c r="F367" s="3"/>
+      <c r="C367" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D367" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E367" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F367" s="11" t="s">
+        <v>62</v>
+      </c>
       <c r="G367" s="3"/>
       <c r="H367" s="3"/>
       <c r="I367" s="3"/>
@@ -28800,7 +31670,7 @@
       <c r="AN373" s="3"/>
       <c r="AO373" s="3"/>
     </row>
-    <row r="374" spans="1:41">
+    <row r="374" ht="14.75" spans="1:41">
       <c r="A374" s="3"/>
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
@@ -28843,12 +31713,18 @@
       <c r="AN374" s="3"/>
       <c r="AO374" s="3"/>
     </row>
-    <row r="375" spans="1:41">
+    <row r="375" ht="14.75" spans="1:41">
       <c r="A375" s="3"/>
       <c r="B375" s="3"/>
-      <c r="C375" s="3"/>
-      <c r="D375" s="3"/>
-      <c r="E375" s="3"/>
+      <c r="C375" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D375" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E375" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="F375" s="3"/>
       <c r="G375" s="3"/>
       <c r="H375" s="3"/>
@@ -28886,12 +31762,18 @@
       <c r="AN375" s="3"/>
       <c r="AO375" s="3"/>
     </row>
-    <row r="376" spans="1:41">
+    <row r="376" ht="14.75" spans="1:41">
       <c r="A376" s="3"/>
       <c r="B376" s="3"/>
-      <c r="C376" s="3"/>
-      <c r="D376" s="3"/>
-      <c r="E376" s="3"/>
+      <c r="C376" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D376" s="10">
+        <v>260</v>
+      </c>
+      <c r="E376" s="10" t="s">
+        <v>63</v>
+      </c>
       <c r="F376" s="3"/>
       <c r="G376" s="3"/>
       <c r="H376" s="3"/>
@@ -28929,12 +31811,18 @@
       <c r="AN376" s="3"/>
       <c r="AO376" s="3"/>
     </row>
-    <row r="377" spans="1:41">
+    <row r="377" ht="14.75" spans="1:41">
       <c r="A377" s="3"/>
       <c r="B377" s="3"/>
-      <c r="C377" s="3"/>
-      <c r="D377" s="3"/>
-      <c r="E377" s="3"/>
+      <c r="C377" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D377" s="10">
+        <v>21</v>
+      </c>
+      <c r="E377" s="10" t="s">
+        <v>64</v>
+      </c>
       <c r="F377" s="3"/>
       <c r="G377" s="3"/>
       <c r="H377" s="3"/>
@@ -28972,12 +31860,18 @@
       <c r="AN377" s="3"/>
       <c r="AO377" s="3"/>
     </row>
-    <row r="378" spans="1:41">
+    <row r="378" ht="14.75" spans="1:41">
       <c r="A378" s="3"/>
       <c r="B378" s="3"/>
-      <c r="C378" s="3"/>
-      <c r="D378" s="3"/>
-      <c r="E378" s="3"/>
+      <c r="C378" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D378" s="10">
+        <v>1</v>
+      </c>
+      <c r="E378" s="11" t="s">
+        <v>65</v>
+      </c>
       <c r="F378" s="3"/>
       <c r="G378" s="3"/>
       <c r="H378" s="3"/>
@@ -29316,7 +32210,7 @@
       <c r="AN385" s="3"/>
       <c r="AO385" s="3"/>
     </row>
-    <row r="386" spans="1:41">
+    <row r="386" ht="14.75" spans="1:41">
       <c r="A386" s="3"/>
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
@@ -29359,13 +32253,21 @@
       <c r="AN386" s="3"/>
       <c r="AO386" s="3"/>
     </row>
-    <row r="387" spans="1:41">
+    <row r="387" ht="14.75" spans="1:41">
       <c r="A387" s="3"/>
       <c r="B387" s="3"/>
-      <c r="C387" s="3"/>
-      <c r="D387" s="3"/>
-      <c r="E387" s="3"/>
-      <c r="F387" s="3"/>
+      <c r="C387" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D387" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E387" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F387" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="G387" s="3"/>
       <c r="H387" s="3"/>
       <c r="I387" s="3"/>
@@ -29402,13 +32304,21 @@
       <c r="AN387" s="3"/>
       <c r="AO387" s="3"/>
     </row>
-    <row r="388" spans="1:41">
+    <row r="388" ht="14.75" spans="1:41">
       <c r="A388" s="3"/>
       <c r="B388" s="3"/>
-      <c r="C388" s="3"/>
-      <c r="D388" s="3"/>
-      <c r="E388" s="3"/>
-      <c r="F388" s="3"/>
+      <c r="C388" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D388" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E388" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F388" s="11" t="s">
+        <v>67</v>
+      </c>
       <c r="G388" s="3"/>
       <c r="H388" s="3"/>
       <c r="I388" s="3"/>
@@ -29445,13 +32355,21 @@
       <c r="AN388" s="3"/>
       <c r="AO388" s="3"/>
     </row>
-    <row r="389" spans="1:41">
+    <row r="389" ht="42.75" spans="1:41">
       <c r="A389" s="3"/>
       <c r="B389" s="3"/>
-      <c r="C389" s="3"/>
-      <c r="D389" s="3"/>
-      <c r="E389" s="3"/>
-      <c r="F389" s="3"/>
+      <c r="C389" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D389" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E389" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F389" s="14" t="s">
+        <v>69</v>
+      </c>
       <c r="G389" s="3"/>
       <c r="H389" s="3"/>
       <c r="I389" s="3"/>
@@ -29488,13 +32406,21 @@
       <c r="AN389" s="3"/>
       <c r="AO389" s="3"/>
     </row>
-    <row r="390" spans="1:41">
+    <row r="390" ht="14.75" spans="1:41">
       <c r="A390" s="3"/>
       <c r="B390" s="3"/>
-      <c r="C390" s="3"/>
-      <c r="D390" s="3"/>
-      <c r="E390" s="3"/>
-      <c r="F390" s="3"/>
+      <c r="C390" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D390" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E390" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F390" s="15" t="s">
+        <v>71</v>
+      </c>
       <c r="G390" s="3"/>
       <c r="H390" s="3"/>
       <c r="I390" s="3"/>
@@ -29531,13 +32457,15 @@
       <c r="AN390" s="3"/>
       <c r="AO390" s="3"/>
     </row>
-    <row r="391" spans="1:41">
+    <row r="391" ht="28.75" spans="1:41">
       <c r="A391" s="3"/>
       <c r="B391" s="3"/>
-      <c r="C391" s="3"/>
-      <c r="D391" s="3"/>
-      <c r="E391" s="3"/>
-      <c r="F391" s="3"/>
+      <c r="C391" s="10"/>
+      <c r="D391" s="10"/>
+      <c r="E391" s="10"/>
+      <c r="F391" s="16" t="s">
+        <v>72</v>
+      </c>
       <c r="G391" s="3"/>
       <c r="H391" s="3"/>
       <c r="I391" s="3"/>
@@ -29574,13 +32502,15 @@
       <c r="AN391" s="3"/>
       <c r="AO391" s="3"/>
     </row>
-    <row r="392" spans="1:41">
+    <row r="392" ht="28.75" spans="1:41">
       <c r="A392" s="3"/>
       <c r="B392" s="3"/>
-      <c r="C392" s="3"/>
-      <c r="D392" s="3"/>
-      <c r="E392" s="3"/>
-      <c r="F392" s="3"/>
+      <c r="C392" s="10"/>
+      <c r="D392" s="10"/>
+      <c r="E392" s="10"/>
+      <c r="F392" s="17" t="s">
+        <v>73</v>
+      </c>
       <c r="G392" s="3"/>
       <c r="H392" s="3"/>
       <c r="I392" s="3"/>
@@ -29618,351 +32548,2106 @@
       <c r="AO392" s="3"/>
     </row>
     <row r="393" spans="1:41">
-      <c r="A393" s="9"/>
-      <c r="B393" s="9"/>
-      <c r="C393" s="9"/>
-      <c r="D393" s="9"/>
-      <c r="E393" s="9"/>
-      <c r="F393" s="9"/>
-      <c r="G393" s="9"/>
-      <c r="H393" s="9"/>
-      <c r="I393" s="9"/>
-      <c r="J393" s="9"/>
-      <c r="K393" s="9"/>
-      <c r="L393" s="9"/>
-      <c r="M393" s="9"/>
-      <c r="N393" s="9"/>
-      <c r="O393" s="9"/>
-      <c r="P393" s="9"/>
-      <c r="Q393" s="9"/>
-      <c r="R393" s="9"/>
-      <c r="S393" s="9"/>
-      <c r="T393" s="9"/>
-      <c r="U393" s="9"/>
-      <c r="V393" s="9"/>
-      <c r="W393" s="9"/>
-      <c r="X393" s="9"/>
-      <c r="Y393" s="9"/>
-      <c r="Z393" s="9"/>
-      <c r="AA393" s="9"/>
-      <c r="AB393" s="9"/>
-      <c r="AC393" s="9"/>
-      <c r="AD393" s="9"/>
-      <c r="AE393" s="9"/>
-      <c r="AF393" s="9"/>
-      <c r="AG393" s="9"/>
-      <c r="AH393" s="9"/>
-      <c r="AI393" s="9"/>
-      <c r="AJ393" s="9"/>
-      <c r="AK393" s="9"/>
-      <c r="AL393" s="9"/>
-      <c r="AM393" s="9"/>
-      <c r="AN393" s="9"/>
-      <c r="AO393" s="9"/>
+      <c r="A393" s="3"/>
+      <c r="B393" s="3"/>
+      <c r="C393" s="3"/>
+      <c r="D393" s="3"/>
+      <c r="E393" s="3"/>
+      <c r="F393" s="3"/>
+      <c r="G393" s="3"/>
+      <c r="H393" s="3"/>
+      <c r="I393" s="3"/>
+      <c r="J393" s="3"/>
+      <c r="K393" s="3"/>
+      <c r="L393" s="3"/>
+      <c r="M393" s="3"/>
+      <c r="N393" s="3"/>
+      <c r="O393" s="3"/>
+      <c r="P393" s="3"/>
+      <c r="Q393" s="3"/>
+      <c r="R393" s="3"/>
+      <c r="S393" s="3"/>
+      <c r="T393" s="3"/>
+      <c r="U393" s="3"/>
+      <c r="V393" s="3"/>
+      <c r="W393" s="3"/>
+      <c r="X393" s="3"/>
+      <c r="Y393" s="3"/>
+      <c r="Z393" s="3"/>
+      <c r="AA393" s="3"/>
+      <c r="AB393" s="3"/>
+      <c r="AC393" s="3"/>
+      <c r="AD393" s="3"/>
+      <c r="AE393" s="3"/>
+      <c r="AF393" s="3"/>
+      <c r="AG393" s="3"/>
+      <c r="AH393" s="3"/>
+      <c r="AI393" s="3"/>
+      <c r="AJ393" s="3"/>
+      <c r="AK393" s="3"/>
+      <c r="AL393" s="3"/>
+      <c r="AM393" s="3"/>
+      <c r="AN393" s="3"/>
+      <c r="AO393" s="3"/>
     </row>
     <row r="394" spans="1:41">
-      <c r="A394" s="9"/>
-      <c r="B394" s="9"/>
-      <c r="C394" s="9"/>
-      <c r="D394" s="9"/>
-      <c r="E394" s="9"/>
-      <c r="F394" s="9"/>
-      <c r="G394" s="9"/>
-      <c r="H394" s="9"/>
-      <c r="I394" s="9"/>
-      <c r="J394" s="9"/>
-      <c r="K394" s="9"/>
-      <c r="L394" s="9"/>
-      <c r="M394" s="9"/>
-      <c r="N394" s="9"/>
-      <c r="O394" s="9"/>
-      <c r="P394" s="9"/>
-      <c r="Q394" s="9"/>
-      <c r="R394" s="9"/>
-      <c r="S394" s="9"/>
-      <c r="T394" s="9"/>
-      <c r="U394" s="9"/>
-      <c r="V394" s="9"/>
-      <c r="W394" s="9"/>
-      <c r="X394" s="9"/>
-      <c r="Y394" s="9"/>
-      <c r="Z394" s="9"/>
-      <c r="AA394" s="9"/>
-      <c r="AB394" s="9"/>
-      <c r="AC394" s="9"/>
-      <c r="AD394" s="9"/>
-      <c r="AE394" s="9"/>
-      <c r="AF394" s="9"/>
-      <c r="AG394" s="9"/>
-      <c r="AH394" s="9"/>
-      <c r="AI394" s="9"/>
-      <c r="AJ394" s="9"/>
-      <c r="AK394" s="9"/>
-      <c r="AL394" s="9"/>
-      <c r="AM394" s="9"/>
-      <c r="AN394" s="9"/>
-      <c r="AO394" s="9"/>
+      <c r="A394" s="3"/>
+      <c r="B394" s="3"/>
+      <c r="C394" s="3"/>
+      <c r="D394" s="3"/>
+      <c r="E394" s="3"/>
+      <c r="F394" s="3"/>
+      <c r="G394" s="3"/>
+      <c r="H394" s="3"/>
+      <c r="I394" s="3"/>
+      <c r="J394" s="3"/>
+      <c r="K394" s="3"/>
+      <c r="L394" s="3"/>
+      <c r="M394" s="3"/>
+      <c r="N394" s="3"/>
+      <c r="O394" s="3"/>
+      <c r="P394" s="3"/>
+      <c r="Q394" s="3"/>
+      <c r="R394" s="3"/>
+      <c r="S394" s="3"/>
+      <c r="T394" s="3"/>
+      <c r="U394" s="3"/>
+      <c r="V394" s="3"/>
+      <c r="W394" s="3"/>
+      <c r="X394" s="3"/>
+      <c r="Y394" s="3"/>
+      <c r="Z394" s="3"/>
+      <c r="AA394" s="3"/>
+      <c r="AB394" s="3"/>
+      <c r="AC394" s="3"/>
+      <c r="AD394" s="3"/>
+      <c r="AE394" s="3"/>
+      <c r="AF394" s="3"/>
+      <c r="AG394" s="3"/>
+      <c r="AH394" s="3"/>
+      <c r="AI394" s="3"/>
+      <c r="AJ394" s="3"/>
+      <c r="AK394" s="3"/>
+      <c r="AL394" s="3"/>
+      <c r="AM394" s="3"/>
+      <c r="AN394" s="3"/>
+      <c r="AO394" s="3"/>
     </row>
     <row r="395" spans="1:41">
-      <c r="A395" s="9"/>
-      <c r="B395" s="9"/>
-      <c r="C395" s="9"/>
-      <c r="D395" s="9"/>
-      <c r="E395" s="9"/>
-      <c r="F395" s="9"/>
-      <c r="G395" s="9"/>
-      <c r="H395" s="9"/>
-      <c r="I395" s="9"/>
-      <c r="J395" s="9"/>
-      <c r="K395" s="9"/>
-      <c r="L395" s="9"/>
-      <c r="M395" s="9"/>
-      <c r="N395" s="9"/>
-      <c r="O395" s="9"/>
-      <c r="P395" s="9"/>
-      <c r="Q395" s="9"/>
-      <c r="R395" s="9"/>
-      <c r="S395" s="9"/>
-      <c r="T395" s="9"/>
-      <c r="U395" s="9"/>
-      <c r="V395" s="9"/>
-      <c r="W395" s="9"/>
-      <c r="X395" s="9"/>
-      <c r="Y395" s="9"/>
-      <c r="Z395" s="9"/>
-      <c r="AA395" s="9"/>
-      <c r="AB395" s="9"/>
-      <c r="AC395" s="9"/>
-      <c r="AD395" s="9"/>
-      <c r="AE395" s="9"/>
-      <c r="AF395" s="9"/>
-      <c r="AG395" s="9"/>
-      <c r="AH395" s="9"/>
-      <c r="AI395" s="9"/>
-      <c r="AJ395" s="9"/>
-      <c r="AK395" s="9"/>
-      <c r="AL395" s="9"/>
-      <c r="AM395" s="9"/>
-      <c r="AN395" s="9"/>
-      <c r="AO395" s="9"/>
+      <c r="A395" s="3"/>
+      <c r="B395" s="3"/>
+      <c r="C395" s="3"/>
+      <c r="D395" s="3"/>
+      <c r="E395" s="3"/>
+      <c r="F395" s="3"/>
+      <c r="G395" s="3"/>
+      <c r="H395" s="3"/>
+      <c r="I395" s="3"/>
+      <c r="J395" s="3"/>
+      <c r="K395" s="3"/>
+      <c r="L395" s="3"/>
+      <c r="M395" s="3"/>
+      <c r="N395" s="3"/>
+      <c r="O395" s="3"/>
+      <c r="P395" s="3"/>
+      <c r="Q395" s="3"/>
+      <c r="R395" s="3"/>
+      <c r="S395" s="3"/>
+      <c r="T395" s="3"/>
+      <c r="U395" s="3"/>
+      <c r="V395" s="3"/>
+      <c r="W395" s="3"/>
+      <c r="X395" s="3"/>
+      <c r="Y395" s="3"/>
+      <c r="Z395" s="3"/>
+      <c r="AA395" s="3"/>
+      <c r="AB395" s="3"/>
+      <c r="AC395" s="3"/>
+      <c r="AD395" s="3"/>
+      <c r="AE395" s="3"/>
+      <c r="AF395" s="3"/>
+      <c r="AG395" s="3"/>
+      <c r="AH395" s="3"/>
+      <c r="AI395" s="3"/>
+      <c r="AJ395" s="3"/>
+      <c r="AK395" s="3"/>
+      <c r="AL395" s="3"/>
+      <c r="AM395" s="3"/>
+      <c r="AN395" s="3"/>
+      <c r="AO395" s="3"/>
     </row>
     <row r="396" spans="1:41">
-      <c r="A396" s="9"/>
-      <c r="B396" s="9"/>
-      <c r="C396" s="9"/>
-      <c r="D396" s="9"/>
-      <c r="E396" s="9"/>
-      <c r="F396" s="9"/>
-      <c r="G396" s="9"/>
-      <c r="H396" s="9"/>
-      <c r="I396" s="9"/>
-      <c r="J396" s="9"/>
-      <c r="K396" s="9"/>
-      <c r="L396" s="9"/>
-      <c r="M396" s="9"/>
-      <c r="N396" s="9"/>
-      <c r="O396" s="9"/>
-      <c r="P396" s="9"/>
-      <c r="Q396" s="9"/>
-      <c r="R396" s="9"/>
-      <c r="S396" s="9"/>
-      <c r="T396" s="9"/>
-      <c r="U396" s="9"/>
-      <c r="V396" s="9"/>
-      <c r="W396" s="9"/>
-      <c r="X396" s="9"/>
-      <c r="Y396" s="9"/>
-      <c r="Z396" s="9"/>
-      <c r="AA396" s="9"/>
-      <c r="AB396" s="9"/>
-      <c r="AC396" s="9"/>
-      <c r="AD396" s="9"/>
-      <c r="AE396" s="9"/>
-      <c r="AF396" s="9"/>
-      <c r="AG396" s="9"/>
-      <c r="AH396" s="9"/>
-      <c r="AI396" s="9"/>
-      <c r="AJ396" s="9"/>
-      <c r="AK396" s="9"/>
-      <c r="AL396" s="9"/>
-      <c r="AM396" s="9"/>
-      <c r="AN396" s="9"/>
-      <c r="AO396" s="9"/>
+      <c r="A396" s="3"/>
+      <c r="B396" s="3"/>
+      <c r="C396" s="3"/>
+      <c r="D396" s="3"/>
+      <c r="E396" s="3"/>
+      <c r="F396" s="3"/>
+      <c r="G396" s="3"/>
+      <c r="H396" s="3"/>
+      <c r="I396" s="3"/>
+      <c r="J396" s="3"/>
+      <c r="K396" s="3"/>
+      <c r="L396" s="3"/>
+      <c r="M396" s="3"/>
+      <c r="N396" s="3"/>
+      <c r="O396" s="3"/>
+      <c r="P396" s="3"/>
+      <c r="Q396" s="3"/>
+      <c r="R396" s="3"/>
+      <c r="S396" s="3"/>
+      <c r="T396" s="3"/>
+      <c r="U396" s="3"/>
+      <c r="V396" s="3"/>
+      <c r="W396" s="3"/>
+      <c r="X396" s="3"/>
+      <c r="Y396" s="3"/>
+      <c r="Z396" s="3"/>
+      <c r="AA396" s="3"/>
+      <c r="AB396" s="3"/>
+      <c r="AC396" s="3"/>
+      <c r="AD396" s="3"/>
+      <c r="AE396" s="3"/>
+      <c r="AF396" s="3"/>
+      <c r="AG396" s="3"/>
+      <c r="AH396" s="3"/>
+      <c r="AI396" s="3"/>
+      <c r="AJ396" s="3"/>
+      <c r="AK396" s="3"/>
+      <c r="AL396" s="3"/>
+      <c r="AM396" s="3"/>
+      <c r="AN396" s="3"/>
+      <c r="AO396" s="3"/>
     </row>
     <row r="397" spans="1:41">
-      <c r="A397" s="9"/>
-      <c r="B397" s="9"/>
-      <c r="C397" s="9"/>
-      <c r="D397" s="9"/>
-      <c r="E397" s="9"/>
-      <c r="F397" s="9"/>
-      <c r="G397" s="9"/>
-      <c r="H397" s="9"/>
-      <c r="I397" s="9"/>
-      <c r="J397" s="9"/>
-      <c r="K397" s="9"/>
-      <c r="L397" s="9"/>
-      <c r="M397" s="9"/>
-      <c r="N397" s="9"/>
-      <c r="O397" s="9"/>
-      <c r="P397" s="9"/>
-      <c r="Q397" s="9"/>
-      <c r="R397" s="9"/>
-      <c r="S397" s="9"/>
-      <c r="T397" s="9"/>
-      <c r="U397" s="9"/>
-      <c r="V397" s="9"/>
-      <c r="W397" s="9"/>
-      <c r="X397" s="9"/>
-      <c r="Y397" s="9"/>
-      <c r="Z397" s="9"/>
-      <c r="AA397" s="9"/>
-      <c r="AB397" s="9"/>
-      <c r="AC397" s="9"/>
-      <c r="AD397" s="9"/>
-      <c r="AE397" s="9"/>
-      <c r="AF397" s="9"/>
-      <c r="AG397" s="9"/>
-      <c r="AH397" s="9"/>
-      <c r="AI397" s="9"/>
-      <c r="AJ397" s="9"/>
-      <c r="AK397" s="9"/>
-      <c r="AL397" s="9"/>
-      <c r="AM397" s="9"/>
-      <c r="AN397" s="9"/>
-      <c r="AO397" s="9"/>
+      <c r="A397" s="3"/>
+      <c r="B397" s="3"/>
+      <c r="C397" s="3"/>
+      <c r="D397" s="3"/>
+      <c r="E397" s="3"/>
+      <c r="F397" s="3"/>
+      <c r="G397" s="3"/>
+      <c r="H397" s="3"/>
+      <c r="I397" s="3"/>
+      <c r="J397" s="3"/>
+      <c r="K397" s="3"/>
+      <c r="L397" s="3"/>
+      <c r="M397" s="3"/>
+      <c r="N397" s="3"/>
+      <c r="O397" s="3"/>
+      <c r="P397" s="3"/>
+      <c r="Q397" s="3"/>
+      <c r="R397" s="3"/>
+      <c r="S397" s="3"/>
+      <c r="T397" s="3"/>
+      <c r="U397" s="3"/>
+      <c r="V397" s="3"/>
+      <c r="W397" s="3"/>
+      <c r="X397" s="3"/>
+      <c r="Y397" s="3"/>
+      <c r="Z397" s="3"/>
+      <c r="AA397" s="3"/>
+      <c r="AB397" s="3"/>
+      <c r="AC397" s="3"/>
+      <c r="AD397" s="3"/>
+      <c r="AE397" s="3"/>
+      <c r="AF397" s="3"/>
+      <c r="AG397" s="3"/>
+      <c r="AH397" s="3"/>
+      <c r="AI397" s="3"/>
+      <c r="AJ397" s="3"/>
+      <c r="AK397" s="3"/>
+      <c r="AL397" s="3"/>
+      <c r="AM397" s="3"/>
+      <c r="AN397" s="3"/>
+      <c r="AO397" s="3"/>
     </row>
     <row r="398" spans="1:41">
-      <c r="A398" s="9"/>
-      <c r="B398" s="9"/>
-      <c r="C398" s="9"/>
-      <c r="D398" s="9"/>
-      <c r="E398" s="9"/>
-      <c r="F398" s="9"/>
-      <c r="G398" s="9"/>
-      <c r="H398" s="9"/>
-      <c r="I398" s="9"/>
-      <c r="J398" s="9"/>
-      <c r="K398" s="9"/>
-      <c r="L398" s="9"/>
-      <c r="M398" s="9"/>
-      <c r="N398" s="9"/>
-      <c r="O398" s="9"/>
-      <c r="P398" s="9"/>
-      <c r="Q398" s="9"/>
-      <c r="R398" s="9"/>
-      <c r="S398" s="9"/>
-      <c r="T398" s="9"/>
-      <c r="U398" s="9"/>
-      <c r="V398" s="9"/>
-      <c r="W398" s="9"/>
-      <c r="X398" s="9"/>
-      <c r="Y398" s="9"/>
-      <c r="Z398" s="9"/>
-      <c r="AA398" s="9"/>
-      <c r="AB398" s="9"/>
-      <c r="AC398" s="9"/>
-      <c r="AD398" s="9"/>
-      <c r="AE398" s="9"/>
-      <c r="AF398" s="9"/>
-      <c r="AG398" s="9"/>
-      <c r="AH398" s="9"/>
-      <c r="AI398" s="9"/>
-      <c r="AJ398" s="9"/>
-      <c r="AK398" s="9"/>
-      <c r="AL398" s="9"/>
-      <c r="AM398" s="9"/>
-      <c r="AN398" s="9"/>
-      <c r="AO398" s="9"/>
+      <c r="A398" s="3"/>
+      <c r="B398" s="3"/>
+      <c r="C398" s="3"/>
+      <c r="D398" s="3"/>
+      <c r="E398" s="3"/>
+      <c r="F398" s="3"/>
+      <c r="G398" s="3"/>
+      <c r="H398" s="3"/>
+      <c r="I398" s="3"/>
+      <c r="J398" s="3"/>
+      <c r="K398" s="3"/>
+      <c r="L398" s="3"/>
+      <c r="M398" s="3"/>
+      <c r="N398" s="3"/>
+      <c r="O398" s="3"/>
+      <c r="P398" s="3"/>
+      <c r="Q398" s="3"/>
+      <c r="R398" s="3"/>
+      <c r="S398" s="3"/>
+      <c r="T398" s="3"/>
+      <c r="U398" s="3"/>
+      <c r="V398" s="3"/>
+      <c r="W398" s="3"/>
+      <c r="X398" s="3"/>
+      <c r="Y398" s="3"/>
+      <c r="Z398" s="3"/>
+      <c r="AA398" s="3"/>
+      <c r="AB398" s="3"/>
+      <c r="AC398" s="3"/>
+      <c r="AD398" s="3"/>
+      <c r="AE398" s="3"/>
+      <c r="AF398" s="3"/>
+      <c r="AG398" s="3"/>
+      <c r="AH398" s="3"/>
+      <c r="AI398" s="3"/>
+      <c r="AJ398" s="3"/>
+      <c r="AK398" s="3"/>
+      <c r="AL398" s="3"/>
+      <c r="AM398" s="3"/>
+      <c r="AN398" s="3"/>
+      <c r="AO398" s="3"/>
     </row>
     <row r="399" spans="1:41">
-      <c r="A399" s="9"/>
-      <c r="B399" s="9"/>
-      <c r="C399" s="9"/>
-      <c r="D399" s="9"/>
-      <c r="E399" s="9"/>
-      <c r="F399" s="9"/>
-      <c r="G399" s="9"/>
-      <c r="H399" s="9"/>
-      <c r="I399" s="9"/>
-      <c r="J399" s="9"/>
-      <c r="K399" s="9"/>
-      <c r="L399" s="9"/>
-      <c r="M399" s="9"/>
-      <c r="N399" s="9"/>
-      <c r="O399" s="9"/>
-      <c r="P399" s="9"/>
-      <c r="Q399" s="9"/>
-      <c r="R399" s="9"/>
-      <c r="S399" s="9"/>
-      <c r="T399" s="9"/>
-      <c r="U399" s="9"/>
-      <c r="V399" s="9"/>
-      <c r="W399" s="9"/>
-      <c r="X399" s="9"/>
-      <c r="Y399" s="9"/>
-      <c r="Z399" s="9"/>
-      <c r="AA399" s="9"/>
-      <c r="AB399" s="9"/>
-      <c r="AC399" s="9"/>
-      <c r="AD399" s="9"/>
-      <c r="AE399" s="9"/>
-      <c r="AF399" s="9"/>
-      <c r="AG399" s="9"/>
-      <c r="AH399" s="9"/>
-      <c r="AI399" s="9"/>
-      <c r="AJ399" s="9"/>
-      <c r="AK399" s="9"/>
-      <c r="AL399" s="9"/>
-      <c r="AM399" s="9"/>
-      <c r="AN399" s="9"/>
-      <c r="AO399" s="9"/>
+      <c r="A399" s="3"/>
+      <c r="B399" s="3"/>
+      <c r="C399" s="3"/>
+      <c r="D399" s="3"/>
+      <c r="E399" s="3"/>
+      <c r="F399" s="3"/>
+      <c r="G399" s="3"/>
+      <c r="H399" s="3"/>
+      <c r="I399" s="3"/>
+      <c r="J399" s="3"/>
+      <c r="K399" s="3"/>
+      <c r="L399" s="3"/>
+      <c r="M399" s="3"/>
+      <c r="N399" s="3"/>
+      <c r="O399" s="3"/>
+      <c r="P399" s="3"/>
+      <c r="Q399" s="3"/>
+      <c r="R399" s="3"/>
+      <c r="S399" s="3"/>
+      <c r="T399" s="3"/>
+      <c r="U399" s="3"/>
+      <c r="V399" s="3"/>
+      <c r="W399" s="3"/>
+      <c r="X399" s="3"/>
+      <c r="Y399" s="3"/>
+      <c r="Z399" s="3"/>
+      <c r="AA399" s="3"/>
+      <c r="AB399" s="3"/>
+      <c r="AC399" s="3"/>
+      <c r="AD399" s="3"/>
+      <c r="AE399" s="3"/>
+      <c r="AF399" s="3"/>
+      <c r="AG399" s="3"/>
+      <c r="AH399" s="3"/>
+      <c r="AI399" s="3"/>
+      <c r="AJ399" s="3"/>
+      <c r="AK399" s="3"/>
+      <c r="AL399" s="3"/>
+      <c r="AM399" s="3"/>
+      <c r="AN399" s="3"/>
+      <c r="AO399" s="3"/>
     </row>
     <row r="400" spans="1:41">
-      <c r="A400" s="9"/>
-      <c r="B400" s="9"/>
-      <c r="C400" s="9"/>
-      <c r="D400" s="9"/>
-      <c r="E400" s="9"/>
-      <c r="F400" s="9"/>
-      <c r="G400" s="9"/>
-      <c r="H400" s="9"/>
-      <c r="I400" s="9"/>
-      <c r="J400" s="9"/>
-      <c r="K400" s="9"/>
-      <c r="L400" s="9"/>
-      <c r="M400" s="9"/>
-      <c r="N400" s="9"/>
-      <c r="O400" s="9"/>
-      <c r="P400" s="9"/>
-      <c r="Q400" s="9"/>
-      <c r="R400" s="9"/>
-      <c r="S400" s="9"/>
-      <c r="T400" s="9"/>
-      <c r="U400" s="9"/>
-      <c r="V400" s="9"/>
-      <c r="W400" s="9"/>
-      <c r="X400" s="9"/>
-      <c r="Y400" s="9"/>
-      <c r="Z400" s="9"/>
-      <c r="AA400" s="9"/>
-      <c r="AB400" s="9"/>
-      <c r="AC400" s="9"/>
-      <c r="AD400" s="9"/>
-      <c r="AE400" s="9"/>
-      <c r="AF400" s="9"/>
-      <c r="AG400" s="9"/>
-      <c r="AH400" s="9"/>
-      <c r="AI400" s="9"/>
-      <c r="AJ400" s="9"/>
-      <c r="AK400" s="9"/>
-      <c r="AL400" s="9"/>
-      <c r="AM400" s="9"/>
-      <c r="AN400" s="9"/>
-      <c r="AO400" s="9"/>
+      <c r="A400" s="3"/>
+      <c r="B400" s="3"/>
+      <c r="C400" s="3"/>
+      <c r="D400" s="3"/>
+      <c r="E400" s="3"/>
+      <c r="F400" s="3"/>
+      <c r="G400" s="3"/>
+      <c r="H400" s="3"/>
+      <c r="I400" s="3"/>
+      <c r="J400" s="3"/>
+      <c r="K400" s="3"/>
+      <c r="L400" s="3"/>
+      <c r="M400" s="3"/>
+      <c r="N400" s="3"/>
+      <c r="O400" s="3"/>
+      <c r="P400" s="3"/>
+      <c r="Q400" s="3"/>
+      <c r="R400" s="3"/>
+      <c r="S400" s="3"/>
+      <c r="T400" s="3"/>
+      <c r="U400" s="3"/>
+      <c r="V400" s="3"/>
+      <c r="W400" s="3"/>
+      <c r="X400" s="3"/>
+      <c r="Y400" s="3"/>
+      <c r="Z400" s="3"/>
+      <c r="AA400" s="3"/>
+      <c r="AB400" s="3"/>
+      <c r="AC400" s="3"/>
+      <c r="AD400" s="3"/>
+      <c r="AE400" s="3"/>
+      <c r="AF400" s="3"/>
+      <c r="AG400" s="3"/>
+      <c r="AH400" s="3"/>
+      <c r="AI400" s="3"/>
+      <c r="AJ400" s="3"/>
+      <c r="AK400" s="3"/>
+      <c r="AL400" s="3"/>
+      <c r="AM400" s="3"/>
+      <c r="AN400" s="3"/>
+      <c r="AO400" s="3"/>
+    </row>
+    <row r="401" spans="1:41">
+      <c r="A401" s="3"/>
+      <c r="B401" s="3"/>
+      <c r="C401" s="3"/>
+      <c r="D401" s="3"/>
+      <c r="E401" s="3"/>
+      <c r="F401" s="3"/>
+      <c r="G401" s="3"/>
+      <c r="H401" s="3"/>
+      <c r="I401" s="3"/>
+      <c r="J401" s="3"/>
+      <c r="K401" s="3"/>
+      <c r="L401" s="3"/>
+      <c r="M401" s="3"/>
+      <c r="N401" s="3"/>
+      <c r="O401" s="3"/>
+      <c r="P401" s="3"/>
+      <c r="Q401" s="3"/>
+      <c r="R401" s="3"/>
+      <c r="S401" s="3"/>
+      <c r="T401" s="3"/>
+      <c r="U401" s="3"/>
+      <c r="V401" s="3"/>
+      <c r="W401" s="3"/>
+      <c r="X401" s="3"/>
+      <c r="Y401" s="3"/>
+      <c r="Z401" s="3"/>
+      <c r="AA401" s="3"/>
+      <c r="AB401" s="3"/>
+      <c r="AC401" s="3"/>
+      <c r="AD401" s="3"/>
+      <c r="AE401" s="3"/>
+      <c r="AF401" s="3"/>
+      <c r="AG401" s="3"/>
+      <c r="AH401" s="3"/>
+      <c r="AI401" s="3"/>
+      <c r="AJ401" s="3"/>
+      <c r="AK401" s="3"/>
+      <c r="AL401" s="3"/>
+      <c r="AM401" s="3"/>
+      <c r="AN401" s="3"/>
+      <c r="AO401" s="3"/>
+    </row>
+    <row r="402" spans="1:41">
+      <c r="A402" s="3"/>
+      <c r="B402" s="3"/>
+      <c r="C402" s="3"/>
+      <c r="D402" s="3"/>
+      <c r="E402" s="3"/>
+      <c r="F402" s="3"/>
+      <c r="G402" s="3"/>
+      <c r="H402" s="3"/>
+      <c r="I402" s="3"/>
+      <c r="J402" s="3"/>
+      <c r="K402" s="3"/>
+      <c r="L402" s="3"/>
+      <c r="M402" s="3"/>
+      <c r="N402" s="3"/>
+      <c r="O402" s="3"/>
+      <c r="P402" s="3"/>
+      <c r="Q402" s="3"/>
+      <c r="R402" s="3"/>
+      <c r="S402" s="3"/>
+      <c r="T402" s="3"/>
+      <c r="U402" s="3"/>
+      <c r="V402" s="3"/>
+      <c r="W402" s="3"/>
+      <c r="X402" s="3"/>
+      <c r="Y402" s="3"/>
+      <c r="Z402" s="3"/>
+      <c r="AA402" s="3"/>
+      <c r="AB402" s="3"/>
+      <c r="AC402" s="3"/>
+      <c r="AD402" s="3"/>
+      <c r="AE402" s="3"/>
+      <c r="AF402" s="3"/>
+      <c r="AG402" s="3"/>
+      <c r="AH402" s="3"/>
+      <c r="AI402" s="3"/>
+      <c r="AJ402" s="3"/>
+      <c r="AK402" s="3"/>
+      <c r="AL402" s="3"/>
+      <c r="AM402" s="3"/>
+      <c r="AN402" s="3"/>
+      <c r="AO402" s="3"/>
+    </row>
+    <row r="403" ht="14.75" spans="1:41">
+      <c r="A403" s="3"/>
+      <c r="B403" s="3"/>
+      <c r="C403" s="3"/>
+      <c r="D403" s="3"/>
+      <c r="E403" s="3"/>
+      <c r="F403" s="3"/>
+      <c r="G403" s="3"/>
+      <c r="H403" s="3"/>
+      <c r="I403" s="3"/>
+      <c r="J403" s="3"/>
+      <c r="K403" s="3"/>
+      <c r="L403" s="3"/>
+      <c r="M403" s="3"/>
+      <c r="N403" s="3"/>
+      <c r="O403" s="3"/>
+      <c r="P403" s="3"/>
+      <c r="Q403" s="3"/>
+      <c r="R403" s="3"/>
+      <c r="S403" s="3"/>
+      <c r="T403" s="3"/>
+      <c r="U403" s="3"/>
+      <c r="V403" s="3"/>
+      <c r="W403" s="3"/>
+      <c r="X403" s="3"/>
+      <c r="Y403" s="3"/>
+      <c r="Z403" s="3"/>
+      <c r="AA403" s="3"/>
+      <c r="AB403" s="3"/>
+      <c r="AC403" s="3"/>
+      <c r="AD403" s="3"/>
+      <c r="AE403" s="3"/>
+      <c r="AF403" s="3"/>
+      <c r="AG403" s="3"/>
+      <c r="AH403" s="3"/>
+      <c r="AI403" s="3"/>
+      <c r="AJ403" s="3"/>
+      <c r="AK403" s="3"/>
+      <c r="AL403" s="3"/>
+      <c r="AM403" s="3"/>
+      <c r="AN403" s="3"/>
+      <c r="AO403" s="3"/>
+    </row>
+    <row r="404" ht="14.75" spans="1:41">
+      <c r="A404" s="3"/>
+      <c r="B404" s="3"/>
+      <c r="C404" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D404" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E404" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F404" s="3"/>
+      <c r="G404" s="3"/>
+      <c r="H404" s="3"/>
+      <c r="I404" s="3"/>
+      <c r="J404" s="3"/>
+      <c r="K404" s="3"/>
+      <c r="L404" s="3"/>
+      <c r="M404" s="3"/>
+      <c r="N404" s="3"/>
+      <c r="O404" s="3"/>
+      <c r="P404" s="3"/>
+      <c r="Q404" s="3"/>
+      <c r="R404" s="3"/>
+      <c r="S404" s="3"/>
+      <c r="T404" s="3"/>
+      <c r="U404" s="3"/>
+      <c r="V404" s="3"/>
+      <c r="W404" s="3"/>
+      <c r="X404" s="3"/>
+      <c r="Y404" s="3"/>
+      <c r="Z404" s="3"/>
+      <c r="AA404" s="3"/>
+      <c r="AB404" s="3"/>
+      <c r="AC404" s="3"/>
+      <c r="AD404" s="3"/>
+      <c r="AE404" s="3"/>
+      <c r="AF404" s="3"/>
+      <c r="AG404" s="3"/>
+      <c r="AH404" s="3"/>
+      <c r="AI404" s="3"/>
+      <c r="AJ404" s="3"/>
+      <c r="AK404" s="3"/>
+      <c r="AL404" s="3"/>
+      <c r="AM404" s="3"/>
+      <c r="AN404" s="3"/>
+      <c r="AO404" s="3"/>
+    </row>
+    <row r="405" ht="14.75" spans="1:41">
+      <c r="A405" s="3"/>
+      <c r="B405" s="3"/>
+      <c r="C405" s="10">
+        <v>1</v>
+      </c>
+      <c r="D405" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E405" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F405" s="3"/>
+      <c r="G405" s="3"/>
+      <c r="H405" s="3"/>
+      <c r="I405" s="3"/>
+      <c r="J405" s="3"/>
+      <c r="K405" s="3"/>
+      <c r="L405" s="3"/>
+      <c r="M405" s="3"/>
+      <c r="N405" s="3"/>
+      <c r="O405" s="3"/>
+      <c r="P405" s="3"/>
+      <c r="Q405" s="3"/>
+      <c r="R405" s="3"/>
+      <c r="S405" s="3"/>
+      <c r="T405" s="3"/>
+      <c r="U405" s="3"/>
+      <c r="V405" s="3"/>
+      <c r="W405" s="3"/>
+      <c r="X405" s="3"/>
+      <c r="Y405" s="3"/>
+      <c r="Z405" s="3"/>
+      <c r="AA405" s="3"/>
+      <c r="AB405" s="3"/>
+      <c r="AC405" s="3"/>
+      <c r="AD405" s="3"/>
+      <c r="AE405" s="3"/>
+      <c r="AF405" s="3"/>
+      <c r="AG405" s="3"/>
+      <c r="AH405" s="3"/>
+      <c r="AI405" s="3"/>
+      <c r="AJ405" s="3"/>
+      <c r="AK405" s="3"/>
+      <c r="AL405" s="3"/>
+      <c r="AM405" s="3"/>
+      <c r="AN405" s="3"/>
+      <c r="AO405" s="3"/>
+    </row>
+    <row r="406" ht="14.75" spans="1:41">
+      <c r="A406" s="3"/>
+      <c r="B406" s="3"/>
+      <c r="C406" s="10">
+        <v>2</v>
+      </c>
+      <c r="D406" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E406" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F406" s="3"/>
+      <c r="G406" s="3"/>
+      <c r="H406" s="3"/>
+      <c r="I406" s="3"/>
+      <c r="J406" s="3"/>
+      <c r="K406" s="3"/>
+      <c r="L406" s="3"/>
+      <c r="M406" s="3"/>
+      <c r="N406" s="3"/>
+      <c r="O406" s="3"/>
+      <c r="P406" s="3"/>
+      <c r="Q406" s="3"/>
+      <c r="R406" s="3"/>
+      <c r="S406" s="3"/>
+      <c r="T406" s="3"/>
+      <c r="U406" s="3"/>
+      <c r="V406" s="3"/>
+      <c r="W406" s="3"/>
+      <c r="X406" s="3"/>
+      <c r="Y406" s="3"/>
+      <c r="Z406" s="3"/>
+      <c r="AA406" s="3"/>
+      <c r="AB406" s="3"/>
+      <c r="AC406" s="3"/>
+      <c r="AD406" s="3"/>
+      <c r="AE406" s="3"/>
+      <c r="AF406" s="3"/>
+      <c r="AG406" s="3"/>
+      <c r="AH406" s="3"/>
+      <c r="AI406" s="3"/>
+      <c r="AJ406" s="3"/>
+      <c r="AK406" s="3"/>
+      <c r="AL406" s="3"/>
+      <c r="AM406" s="3"/>
+      <c r="AN406" s="3"/>
+      <c r="AO406" s="3"/>
+    </row>
+    <row r="407" ht="28.75" spans="1:41">
+      <c r="A407" s="3"/>
+      <c r="B407" s="3"/>
+      <c r="C407" s="10">
+        <v>3</v>
+      </c>
+      <c r="D407" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E407" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F407" s="3"/>
+      <c r="G407" s="3"/>
+      <c r="H407" s="3"/>
+      <c r="I407" s="3"/>
+      <c r="J407" s="3"/>
+      <c r="K407" s="3"/>
+      <c r="L407" s="3"/>
+      <c r="M407" s="3"/>
+      <c r="N407" s="3"/>
+      <c r="O407" s="3"/>
+      <c r="P407" s="3"/>
+      <c r="Q407" s="3"/>
+      <c r="R407" s="3"/>
+      <c r="S407" s="3"/>
+      <c r="T407" s="3"/>
+      <c r="U407" s="3"/>
+      <c r="V407" s="3"/>
+      <c r="W407" s="3"/>
+      <c r="X407" s="3"/>
+      <c r="Y407" s="3"/>
+      <c r="Z407" s="3"/>
+      <c r="AA407" s="3"/>
+      <c r="AB407" s="3"/>
+      <c r="AC407" s="3"/>
+      <c r="AD407" s="3"/>
+      <c r="AE407" s="3"/>
+      <c r="AF407" s="3"/>
+      <c r="AG407" s="3"/>
+      <c r="AH407" s="3"/>
+      <c r="AI407" s="3"/>
+      <c r="AJ407" s="3"/>
+      <c r="AK407" s="3"/>
+      <c r="AL407" s="3"/>
+      <c r="AM407" s="3"/>
+      <c r="AN407" s="3"/>
+      <c r="AO407" s="3"/>
+    </row>
+    <row r="408" ht="28.75" spans="1:41">
+      <c r="A408" s="3"/>
+      <c r="B408" s="3"/>
+      <c r="C408" s="10">
+        <v>4</v>
+      </c>
+      <c r="D408" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E408" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F408" s="3"/>
+      <c r="G408" s="3"/>
+      <c r="H408" s="3"/>
+      <c r="I408" s="3"/>
+      <c r="J408" s="3"/>
+      <c r="K408" s="3"/>
+      <c r="L408" s="3"/>
+      <c r="M408" s="3"/>
+      <c r="N408" s="3"/>
+      <c r="O408" s="3"/>
+      <c r="P408" s="3"/>
+      <c r="Q408" s="3"/>
+      <c r="R408" s="3"/>
+      <c r="S408" s="3"/>
+      <c r="T408" s="3"/>
+      <c r="U408" s="3"/>
+      <c r="V408" s="3"/>
+      <c r="W408" s="3"/>
+      <c r="X408" s="3"/>
+      <c r="Y408" s="3"/>
+      <c r="Z408" s="3"/>
+      <c r="AA408" s="3"/>
+      <c r="AB408" s="3"/>
+      <c r="AC408" s="3"/>
+      <c r="AD408" s="3"/>
+      <c r="AE408" s="3"/>
+      <c r="AF408" s="3"/>
+      <c r="AG408" s="3"/>
+      <c r="AH408" s="3"/>
+      <c r="AI408" s="3"/>
+      <c r="AJ408" s="3"/>
+      <c r="AK408" s="3"/>
+      <c r="AL408" s="3"/>
+      <c r="AM408" s="3"/>
+      <c r="AN408" s="3"/>
+      <c r="AO408" s="3"/>
+    </row>
+    <row r="409" ht="28.75" spans="1:41">
+      <c r="A409" s="3"/>
+      <c r="B409" s="3"/>
+      <c r="C409" s="10">
+        <v>5</v>
+      </c>
+      <c r="D409" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E409" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="F409" s="3"/>
+      <c r="G409" s="3"/>
+      <c r="H409" s="3"/>
+      <c r="I409" s="3"/>
+      <c r="J409" s="3"/>
+      <c r="K409" s="3"/>
+      <c r="L409" s="3"/>
+      <c r="M409" s="3"/>
+      <c r="N409" s="3"/>
+      <c r="O409" s="3"/>
+      <c r="P409" s="3"/>
+      <c r="Q409" s="3"/>
+      <c r="R409" s="3"/>
+      <c r="S409" s="3"/>
+      <c r="T409" s="3"/>
+      <c r="U409" s="3"/>
+      <c r="V409" s="3"/>
+      <c r="W409" s="3"/>
+      <c r="X409" s="3"/>
+      <c r="Y409" s="3"/>
+      <c r="Z409" s="3"/>
+      <c r="AA409" s="3"/>
+      <c r="AB409" s="3"/>
+      <c r="AC409" s="3"/>
+      <c r="AD409" s="3"/>
+      <c r="AE409" s="3"/>
+      <c r="AF409" s="3"/>
+      <c r="AG409" s="3"/>
+      <c r="AH409" s="3"/>
+      <c r="AI409" s="3"/>
+      <c r="AJ409" s="3"/>
+      <c r="AK409" s="3"/>
+      <c r="AL409" s="3"/>
+      <c r="AM409" s="3"/>
+      <c r="AN409" s="3"/>
+      <c r="AO409" s="3"/>
+    </row>
+    <row r="410" spans="1:41">
+      <c r="A410" s="3"/>
+      <c r="B410" s="3"/>
+      <c r="C410" s="3"/>
+      <c r="D410" s="3"/>
+      <c r="E410" s="3"/>
+      <c r="F410" s="3"/>
+      <c r="G410" s="3"/>
+      <c r="H410" s="3"/>
+      <c r="I410" s="3"/>
+      <c r="J410" s="3"/>
+      <c r="K410" s="3"/>
+      <c r="L410" s="3"/>
+      <c r="M410" s="3"/>
+      <c r="N410" s="3"/>
+      <c r="O410" s="3"/>
+      <c r="P410" s="3"/>
+      <c r="Q410" s="3"/>
+      <c r="R410" s="3"/>
+      <c r="S410" s="3"/>
+      <c r="T410" s="3"/>
+      <c r="U410" s="3"/>
+      <c r="V410" s="3"/>
+      <c r="W410" s="3"/>
+      <c r="X410" s="3"/>
+      <c r="Y410" s="3"/>
+      <c r="Z410" s="3"/>
+      <c r="AA410" s="3"/>
+      <c r="AB410" s="3"/>
+      <c r="AC410" s="3"/>
+      <c r="AD410" s="3"/>
+      <c r="AE410" s="3"/>
+      <c r="AF410" s="3"/>
+      <c r="AG410" s="3"/>
+      <c r="AH410" s="3"/>
+      <c r="AI410" s="3"/>
+      <c r="AJ410" s="3"/>
+      <c r="AK410" s="3"/>
+      <c r="AL410" s="3"/>
+      <c r="AM410" s="3"/>
+      <c r="AN410" s="3"/>
+      <c r="AO410" s="3"/>
+    </row>
+    <row r="411" spans="1:41">
+      <c r="A411" s="3"/>
+      <c r="B411" s="3"/>
+      <c r="C411" s="3"/>
+      <c r="D411" s="3"/>
+      <c r="E411" s="3"/>
+      <c r="F411" s="3"/>
+      <c r="G411" s="3"/>
+      <c r="H411" s="3"/>
+      <c r="I411" s="3"/>
+      <c r="J411" s="3"/>
+      <c r="K411" s="3"/>
+      <c r="L411" s="3"/>
+      <c r="M411" s="3"/>
+      <c r="N411" s="3"/>
+      <c r="O411" s="3"/>
+      <c r="P411" s="3"/>
+      <c r="Q411" s="3"/>
+      <c r="R411" s="3"/>
+      <c r="S411" s="3"/>
+      <c r="T411" s="3"/>
+      <c r="U411" s="3"/>
+      <c r="V411" s="3"/>
+      <c r="W411" s="3"/>
+      <c r="X411" s="3"/>
+      <c r="Y411" s="3"/>
+      <c r="Z411" s="3"/>
+      <c r="AA411" s="3"/>
+      <c r="AB411" s="3"/>
+      <c r="AC411" s="3"/>
+      <c r="AD411" s="3"/>
+      <c r="AE411" s="3"/>
+      <c r="AF411" s="3"/>
+      <c r="AG411" s="3"/>
+      <c r="AH411" s="3"/>
+      <c r="AI411" s="3"/>
+      <c r="AJ411" s="3"/>
+      <c r="AK411" s="3"/>
+      <c r="AL411" s="3"/>
+      <c r="AM411" s="3"/>
+      <c r="AN411" s="3"/>
+      <c r="AO411" s="3"/>
+    </row>
+    <row r="412" spans="1:41">
+      <c r="A412" s="3"/>
+      <c r="B412" s="3"/>
+      <c r="C412" s="3"/>
+      <c r="D412" s="3"/>
+      <c r="E412" s="3"/>
+      <c r="F412" s="3"/>
+      <c r="G412" s="3"/>
+      <c r="H412" s="3"/>
+      <c r="I412" s="3"/>
+      <c r="J412" s="3"/>
+      <c r="K412" s="3"/>
+      <c r="L412" s="3"/>
+      <c r="M412" s="3"/>
+      <c r="N412" s="3"/>
+      <c r="O412" s="3"/>
+      <c r="P412" s="3"/>
+      <c r="Q412" s="3"/>
+      <c r="R412" s="3"/>
+      <c r="S412" s="3"/>
+      <c r="T412" s="3"/>
+      <c r="U412" s="3"/>
+      <c r="V412" s="3"/>
+      <c r="W412" s="3"/>
+      <c r="X412" s="3"/>
+      <c r="Y412" s="3"/>
+      <c r="Z412" s="3"/>
+      <c r="AA412" s="3"/>
+      <c r="AB412" s="3"/>
+      <c r="AC412" s="3"/>
+      <c r="AD412" s="3"/>
+      <c r="AE412" s="3"/>
+      <c r="AF412" s="3"/>
+      <c r="AG412" s="3"/>
+      <c r="AH412" s="3"/>
+      <c r="AI412" s="3"/>
+      <c r="AJ412" s="3"/>
+      <c r="AK412" s="3"/>
+      <c r="AL412" s="3"/>
+      <c r="AM412" s="3"/>
+      <c r="AN412" s="3"/>
+      <c r="AO412" s="3"/>
+    </row>
+    <row r="413" spans="1:41">
+      <c r="A413" s="3"/>
+      <c r="B413" s="3"/>
+      <c r="C413" s="3"/>
+      <c r="D413" s="3"/>
+      <c r="E413" s="3"/>
+      <c r="F413" s="3"/>
+      <c r="G413" s="3"/>
+      <c r="H413" s="3"/>
+      <c r="I413" s="3"/>
+      <c r="J413" s="3"/>
+      <c r="K413" s="3"/>
+      <c r="L413" s="3"/>
+      <c r="M413" s="3"/>
+      <c r="N413" s="3"/>
+      <c r="O413" s="3"/>
+      <c r="P413" s="3"/>
+      <c r="Q413" s="3"/>
+      <c r="R413" s="3"/>
+      <c r="S413" s="3"/>
+      <c r="T413" s="3"/>
+      <c r="U413" s="3"/>
+      <c r="V413" s="3"/>
+      <c r="W413" s="3"/>
+      <c r="X413" s="3"/>
+      <c r="Y413" s="3"/>
+      <c r="Z413" s="3"/>
+      <c r="AA413" s="3"/>
+      <c r="AB413" s="3"/>
+      <c r="AC413" s="3"/>
+      <c r="AD413" s="3"/>
+      <c r="AE413" s="3"/>
+      <c r="AF413" s="3"/>
+      <c r="AG413" s="3"/>
+      <c r="AH413" s="3"/>
+      <c r="AI413" s="3"/>
+      <c r="AJ413" s="3"/>
+      <c r="AK413" s="3"/>
+      <c r="AL413" s="3"/>
+      <c r="AM413" s="3"/>
+      <c r="AN413" s="3"/>
+      <c r="AO413" s="3"/>
+    </row>
+    <row r="414" spans="1:41">
+      <c r="A414" s="3"/>
+      <c r="B414" s="3"/>
+      <c r="C414" s="3"/>
+      <c r="D414" s="3"/>
+      <c r="E414" s="3"/>
+      <c r="F414" s="3"/>
+      <c r="G414" s="3"/>
+      <c r="H414" s="3"/>
+      <c r="I414" s="3"/>
+      <c r="J414" s="3"/>
+      <c r="K414" s="3"/>
+      <c r="L414" s="3"/>
+      <c r="M414" s="3"/>
+      <c r="N414" s="3"/>
+      <c r="O414" s="3"/>
+      <c r="P414" s="3"/>
+      <c r="Q414" s="3"/>
+      <c r="R414" s="3"/>
+      <c r="S414" s="3"/>
+      <c r="T414" s="3"/>
+      <c r="U414" s="3"/>
+      <c r="V414" s="3"/>
+      <c r="W414" s="3"/>
+      <c r="X414" s="3"/>
+      <c r="Y414" s="3"/>
+      <c r="Z414" s="3"/>
+      <c r="AA414" s="3"/>
+      <c r="AB414" s="3"/>
+      <c r="AC414" s="3"/>
+      <c r="AD414" s="3"/>
+      <c r="AE414" s="3"/>
+      <c r="AF414" s="3"/>
+      <c r="AG414" s="3"/>
+      <c r="AH414" s="3"/>
+      <c r="AI414" s="3"/>
+      <c r="AJ414" s="3"/>
+      <c r="AK414" s="3"/>
+      <c r="AL414" s="3"/>
+      <c r="AM414" s="3"/>
+      <c r="AN414" s="3"/>
+      <c r="AO414" s="3"/>
+    </row>
+    <row r="415" spans="1:41">
+      <c r="A415" s="3"/>
+      <c r="B415" s="3"/>
+      <c r="C415" s="3"/>
+      <c r="D415" s="3"/>
+      <c r="E415" s="3"/>
+      <c r="F415" s="3"/>
+      <c r="G415" s="3"/>
+      <c r="H415" s="3"/>
+      <c r="I415" s="3"/>
+      <c r="J415" s="3"/>
+      <c r="K415" s="3"/>
+      <c r="L415" s="3"/>
+      <c r="M415" s="3"/>
+      <c r="N415" s="3"/>
+      <c r="O415" s="3"/>
+      <c r="P415" s="3"/>
+      <c r="Q415" s="3"/>
+      <c r="R415" s="3"/>
+      <c r="S415" s="3"/>
+      <c r="T415" s="3"/>
+      <c r="U415" s="3"/>
+      <c r="V415" s="3"/>
+      <c r="W415" s="3"/>
+      <c r="X415" s="3"/>
+      <c r="Y415" s="3"/>
+      <c r="Z415" s="3"/>
+      <c r="AA415" s="3"/>
+      <c r="AB415" s="3"/>
+      <c r="AC415" s="3"/>
+      <c r="AD415" s="3"/>
+      <c r="AE415" s="3"/>
+      <c r="AF415" s="3"/>
+      <c r="AG415" s="3"/>
+      <c r="AH415" s="3"/>
+      <c r="AI415" s="3"/>
+      <c r="AJ415" s="3"/>
+      <c r="AK415" s="3"/>
+      <c r="AL415" s="3"/>
+      <c r="AM415" s="3"/>
+      <c r="AN415" s="3"/>
+      <c r="AO415" s="3"/>
+    </row>
+    <row r="416" ht="14.75" spans="1:41">
+      <c r="A416" s="3"/>
+      <c r="B416" s="3"/>
+      <c r="C416" s="3"/>
+      <c r="D416" s="3"/>
+      <c r="E416" s="3"/>
+      <c r="F416" s="3"/>
+      <c r="G416" s="3"/>
+      <c r="H416" s="3"/>
+      <c r="I416" s="3"/>
+      <c r="J416" s="3"/>
+      <c r="K416" s="3"/>
+      <c r="L416" s="3"/>
+      <c r="M416" s="3"/>
+      <c r="N416" s="3"/>
+      <c r="O416" s="3"/>
+      <c r="P416" s="3"/>
+      <c r="Q416" s="3"/>
+      <c r="R416" s="3"/>
+      <c r="S416" s="3"/>
+      <c r="T416" s="3"/>
+      <c r="U416" s="3"/>
+      <c r="V416" s="3"/>
+      <c r="W416" s="3"/>
+      <c r="X416" s="3"/>
+      <c r="Y416" s="3"/>
+      <c r="Z416" s="3"/>
+      <c r="AA416" s="3"/>
+      <c r="AB416" s="3"/>
+      <c r="AC416" s="3"/>
+      <c r="AD416" s="3"/>
+      <c r="AE416" s="3"/>
+      <c r="AF416" s="3"/>
+      <c r="AG416" s="3"/>
+      <c r="AH416" s="3"/>
+      <c r="AI416" s="3"/>
+      <c r="AJ416" s="3"/>
+      <c r="AK416" s="3"/>
+      <c r="AL416" s="3"/>
+      <c r="AM416" s="3"/>
+      <c r="AN416" s="3"/>
+      <c r="AO416" s="3"/>
+    </row>
+    <row r="417" ht="14.75" spans="1:41">
+      <c r="A417" s="3"/>
+      <c r="B417" s="3"/>
+      <c r="C417" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D417" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E417" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F417" s="3"/>
+      <c r="G417" s="3"/>
+      <c r="H417" s="3"/>
+      <c r="I417" s="3"/>
+      <c r="J417" s="3"/>
+      <c r="K417" s="3"/>
+      <c r="L417" s="3"/>
+      <c r="M417" s="3"/>
+      <c r="N417" s="3"/>
+      <c r="O417" s="3"/>
+      <c r="P417" s="3"/>
+      <c r="Q417" s="3"/>
+      <c r="R417" s="3"/>
+      <c r="S417" s="3"/>
+      <c r="T417" s="3"/>
+      <c r="U417" s="3"/>
+      <c r="V417" s="3"/>
+      <c r="W417" s="3"/>
+      <c r="X417" s="3"/>
+      <c r="Y417" s="3"/>
+      <c r="Z417" s="3"/>
+      <c r="AA417" s="3"/>
+      <c r="AB417" s="3"/>
+      <c r="AC417" s="3"/>
+      <c r="AD417" s="3"/>
+      <c r="AE417" s="3"/>
+      <c r="AF417" s="3"/>
+      <c r="AG417" s="3"/>
+      <c r="AH417" s="3"/>
+      <c r="AI417" s="3"/>
+      <c r="AJ417" s="3"/>
+      <c r="AK417" s="3"/>
+      <c r="AL417" s="3"/>
+      <c r="AM417" s="3"/>
+      <c r="AN417" s="3"/>
+      <c r="AO417" s="3"/>
+    </row>
+    <row r="418" ht="28.75" spans="1:41">
+      <c r="A418" s="3"/>
+      <c r="B418" s="3"/>
+      <c r="C418" s="10">
+        <v>6</v>
+      </c>
+      <c r="D418" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E418" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="F418" s="3"/>
+      <c r="G418" s="3"/>
+      <c r="H418" s="3"/>
+      <c r="I418" s="3"/>
+      <c r="J418" s="3"/>
+      <c r="K418" s="3"/>
+      <c r="L418" s="3"/>
+      <c r="M418" s="3"/>
+      <c r="N418" s="3"/>
+      <c r="O418" s="3"/>
+      <c r="P418" s="3"/>
+      <c r="Q418" s="3"/>
+      <c r="R418" s="3"/>
+      <c r="S418" s="3"/>
+      <c r="T418" s="3"/>
+      <c r="U418" s="3"/>
+      <c r="V418" s="3"/>
+      <c r="W418" s="3"/>
+      <c r="X418" s="3"/>
+      <c r="Y418" s="3"/>
+      <c r="Z418" s="3"/>
+      <c r="AA418" s="3"/>
+      <c r="AB418" s="3"/>
+      <c r="AC418" s="3"/>
+      <c r="AD418" s="3"/>
+      <c r="AE418" s="3"/>
+      <c r="AF418" s="3"/>
+      <c r="AG418" s="3"/>
+      <c r="AH418" s="3"/>
+      <c r="AI418" s="3"/>
+      <c r="AJ418" s="3"/>
+      <c r="AK418" s="3"/>
+      <c r="AL418" s="3"/>
+      <c r="AM418" s="3"/>
+      <c r="AN418" s="3"/>
+      <c r="AO418" s="3"/>
+    </row>
+    <row r="419" ht="14.75" spans="1:41">
+      <c r="A419" s="3"/>
+      <c r="B419" s="3"/>
+      <c r="C419" s="10">
+        <v>7</v>
+      </c>
+      <c r="D419" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E419" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F419" s="3"/>
+      <c r="G419" s="3"/>
+      <c r="H419" s="3"/>
+      <c r="I419" s="3"/>
+      <c r="J419" s="3"/>
+      <c r="K419" s="3"/>
+      <c r="L419" s="3"/>
+      <c r="M419" s="3"/>
+      <c r="N419" s="3"/>
+      <c r="O419" s="3"/>
+      <c r="P419" s="3"/>
+      <c r="Q419" s="3"/>
+      <c r="R419" s="3"/>
+      <c r="S419" s="3"/>
+      <c r="T419" s="3"/>
+      <c r="U419" s="3"/>
+      <c r="V419" s="3"/>
+      <c r="W419" s="3"/>
+      <c r="X419" s="3"/>
+      <c r="Y419" s="3"/>
+      <c r="Z419" s="3"/>
+      <c r="AA419" s="3"/>
+      <c r="AB419" s="3"/>
+      <c r="AC419" s="3"/>
+      <c r="AD419" s="3"/>
+      <c r="AE419" s="3"/>
+      <c r="AF419" s="3"/>
+      <c r="AG419" s="3"/>
+      <c r="AH419" s="3"/>
+      <c r="AI419" s="3"/>
+      <c r="AJ419" s="3"/>
+      <c r="AK419" s="3"/>
+      <c r="AL419" s="3"/>
+      <c r="AM419" s="3"/>
+      <c r="AN419" s="3"/>
+      <c r="AO419" s="3"/>
+    </row>
+    <row r="420" ht="28.75" spans="1:41">
+      <c r="A420" s="3"/>
+      <c r="B420" s="3"/>
+      <c r="C420" s="10">
+        <v>8</v>
+      </c>
+      <c r="D420" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E420" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="F420" s="3"/>
+      <c r="G420" s="3"/>
+      <c r="H420" s="3"/>
+      <c r="I420" s="3"/>
+      <c r="J420" s="3"/>
+      <c r="K420" s="3"/>
+      <c r="L420" s="3"/>
+      <c r="M420" s="3"/>
+      <c r="N420" s="3"/>
+      <c r="O420" s="3"/>
+      <c r="P420" s="3"/>
+      <c r="Q420" s="3"/>
+      <c r="R420" s="3"/>
+      <c r="S420" s="3"/>
+      <c r="T420" s="3"/>
+      <c r="U420" s="3"/>
+      <c r="V420" s="3"/>
+      <c r="W420" s="3"/>
+      <c r="X420" s="3"/>
+      <c r="Y420" s="3"/>
+      <c r="Z420" s="3"/>
+      <c r="AA420" s="3"/>
+      <c r="AB420" s="3"/>
+      <c r="AC420" s="3"/>
+      <c r="AD420" s="3"/>
+      <c r="AE420" s="3"/>
+      <c r="AF420" s="3"/>
+      <c r="AG420" s="3"/>
+      <c r="AH420" s="3"/>
+      <c r="AI420" s="3"/>
+      <c r="AJ420" s="3"/>
+      <c r="AK420" s="3"/>
+      <c r="AL420" s="3"/>
+      <c r="AM420" s="3"/>
+      <c r="AN420" s="3"/>
+      <c r="AO420" s="3"/>
+    </row>
+    <row r="421" ht="14.75" spans="1:41">
+      <c r="A421" s="3"/>
+      <c r="B421" s="3"/>
+      <c r="C421" s="10">
+        <v>9</v>
+      </c>
+      <c r="D421" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E421" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="F421" s="3"/>
+      <c r="G421" s="3"/>
+      <c r="H421" s="3"/>
+      <c r="I421" s="3"/>
+      <c r="J421" s="3"/>
+      <c r="K421" s="3"/>
+      <c r="L421" s="3"/>
+      <c r="M421" s="3"/>
+      <c r="N421" s="3"/>
+      <c r="O421" s="3"/>
+      <c r="P421" s="3"/>
+      <c r="Q421" s="3"/>
+      <c r="R421" s="3"/>
+      <c r="S421" s="3"/>
+      <c r="T421" s="3"/>
+      <c r="U421" s="3"/>
+      <c r="V421" s="3"/>
+      <c r="W421" s="3"/>
+      <c r="X421" s="3"/>
+      <c r="Y421" s="3"/>
+      <c r="Z421" s="3"/>
+      <c r="AA421" s="3"/>
+      <c r="AB421" s="3"/>
+      <c r="AC421" s="3"/>
+      <c r="AD421" s="3"/>
+      <c r="AE421" s="3"/>
+      <c r="AF421" s="3"/>
+      <c r="AG421" s="3"/>
+      <c r="AH421" s="3"/>
+      <c r="AI421" s="3"/>
+      <c r="AJ421" s="3"/>
+      <c r="AK421" s="3"/>
+      <c r="AL421" s="3"/>
+      <c r="AM421" s="3"/>
+      <c r="AN421" s="3"/>
+      <c r="AO421" s="3"/>
+    </row>
+    <row r="422" ht="28.75" spans="1:41">
+      <c r="A422" s="3"/>
+      <c r="B422" s="3"/>
+      <c r="C422" s="10">
+        <v>10</v>
+      </c>
+      <c r="D422" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E422" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F422" s="3"/>
+      <c r="G422" s="3"/>
+      <c r="H422" s="3"/>
+      <c r="I422" s="3"/>
+      <c r="J422" s="3"/>
+      <c r="K422" s="3"/>
+      <c r="L422" s="3"/>
+      <c r="M422" s="3"/>
+      <c r="N422" s="3"/>
+      <c r="O422" s="3"/>
+      <c r="P422" s="3"/>
+      <c r="Q422" s="3"/>
+      <c r="R422" s="3"/>
+      <c r="S422" s="3"/>
+      <c r="T422" s="3"/>
+      <c r="U422" s="3"/>
+      <c r="V422" s="3"/>
+      <c r="W422" s="3"/>
+      <c r="X422" s="3"/>
+      <c r="Y422" s="3"/>
+      <c r="Z422" s="3"/>
+      <c r="AA422" s="3"/>
+      <c r="AB422" s="3"/>
+      <c r="AC422" s="3"/>
+      <c r="AD422" s="3"/>
+      <c r="AE422" s="3"/>
+      <c r="AF422" s="3"/>
+      <c r="AG422" s="3"/>
+      <c r="AH422" s="3"/>
+      <c r="AI422" s="3"/>
+      <c r="AJ422" s="3"/>
+      <c r="AK422" s="3"/>
+      <c r="AL422" s="3"/>
+      <c r="AM422" s="3"/>
+      <c r="AN422" s="3"/>
+      <c r="AO422" s="3"/>
+    </row>
+    <row r="423" spans="1:41">
+      <c r="A423" s="3"/>
+      <c r="B423" s="3"/>
+      <c r="C423" s="3"/>
+      <c r="D423" s="3"/>
+      <c r="E423" s="3"/>
+      <c r="F423" s="3"/>
+      <c r="G423" s="3"/>
+      <c r="H423" s="3"/>
+      <c r="I423" s="3"/>
+      <c r="J423" s="3"/>
+      <c r="K423" s="3"/>
+      <c r="L423" s="3"/>
+      <c r="M423" s="3"/>
+      <c r="N423" s="3"/>
+      <c r="O423" s="3"/>
+      <c r="P423" s="3"/>
+      <c r="Q423" s="3"/>
+      <c r="R423" s="3"/>
+      <c r="S423" s="3"/>
+      <c r="T423" s="3"/>
+      <c r="U423" s="3"/>
+      <c r="V423" s="3"/>
+      <c r="W423" s="3"/>
+      <c r="X423" s="3"/>
+      <c r="Y423" s="3"/>
+      <c r="Z423" s="3"/>
+      <c r="AA423" s="3"/>
+      <c r="AB423" s="3"/>
+      <c r="AC423" s="3"/>
+      <c r="AD423" s="3"/>
+      <c r="AE423" s="3"/>
+      <c r="AF423" s="3"/>
+      <c r="AG423" s="3"/>
+      <c r="AH423" s="3"/>
+      <c r="AI423" s="3"/>
+      <c r="AJ423" s="3"/>
+      <c r="AK423" s="3"/>
+      <c r="AL423" s="3"/>
+      <c r="AM423" s="3"/>
+      <c r="AN423" s="3"/>
+      <c r="AO423" s="3"/>
+    </row>
+    <row r="424" spans="1:41">
+      <c r="A424" s="3"/>
+      <c r="B424" s="3"/>
+      <c r="C424" s="3"/>
+      <c r="D424" s="3"/>
+      <c r="E424" s="3"/>
+      <c r="F424" s="3"/>
+      <c r="G424" s="3"/>
+      <c r="H424" s="3"/>
+      <c r="I424" s="3"/>
+      <c r="J424" s="3"/>
+      <c r="K424" s="3"/>
+      <c r="L424" s="3"/>
+      <c r="M424" s="3"/>
+      <c r="N424" s="3"/>
+      <c r="O424" s="3"/>
+      <c r="P424" s="3"/>
+      <c r="Q424" s="3"/>
+      <c r="R424" s="3"/>
+      <c r="S424" s="3"/>
+      <c r="T424" s="3"/>
+      <c r="U424" s="3"/>
+      <c r="V424" s="3"/>
+      <c r="W424" s="3"/>
+      <c r="X424" s="3"/>
+      <c r="Y424" s="3"/>
+      <c r="Z424" s="3"/>
+      <c r="AA424" s="3"/>
+      <c r="AB424" s="3"/>
+      <c r="AC424" s="3"/>
+      <c r="AD424" s="3"/>
+      <c r="AE424" s="3"/>
+      <c r="AF424" s="3"/>
+      <c r="AG424" s="3"/>
+      <c r="AH424" s="3"/>
+      <c r="AI424" s="3"/>
+      <c r="AJ424" s="3"/>
+      <c r="AK424" s="3"/>
+      <c r="AL424" s="3"/>
+      <c r="AM424" s="3"/>
+      <c r="AN424" s="3"/>
+      <c r="AO424" s="3"/>
+    </row>
+    <row r="425" spans="1:41">
+      <c r="A425" s="3"/>
+      <c r="B425" s="3"/>
+      <c r="C425" s="3"/>
+      <c r="D425" s="3"/>
+      <c r="E425" s="3"/>
+      <c r="F425" s="3"/>
+      <c r="G425" s="3"/>
+      <c r="H425" s="3"/>
+      <c r="I425" s="3"/>
+      <c r="J425" s="3"/>
+      <c r="K425" s="3"/>
+      <c r="L425" s="3"/>
+      <c r="M425" s="3"/>
+      <c r="N425" s="3"/>
+      <c r="O425" s="3"/>
+      <c r="P425" s="3"/>
+      <c r="Q425" s="3"/>
+      <c r="R425" s="3"/>
+      <c r="S425" s="3"/>
+      <c r="T425" s="3"/>
+      <c r="U425" s="3"/>
+      <c r="V425" s="3"/>
+      <c r="W425" s="3"/>
+      <c r="X425" s="3"/>
+      <c r="Y425" s="3"/>
+      <c r="Z425" s="3"/>
+      <c r="AA425" s="3"/>
+      <c r="AB425" s="3"/>
+      <c r="AC425" s="3"/>
+      <c r="AD425" s="3"/>
+      <c r="AE425" s="3"/>
+      <c r="AF425" s="3"/>
+      <c r="AG425" s="3"/>
+      <c r="AH425" s="3"/>
+      <c r="AI425" s="3"/>
+      <c r="AJ425" s="3"/>
+      <c r="AK425" s="3"/>
+      <c r="AL425" s="3"/>
+      <c r="AM425" s="3"/>
+      <c r="AN425" s="3"/>
+      <c r="AO425" s="3"/>
+    </row>
+    <row r="426" spans="1:41">
+      <c r="A426" s="3"/>
+      <c r="B426" s="3"/>
+      <c r="C426" s="3"/>
+      <c r="D426" s="3"/>
+      <c r="E426" s="3"/>
+      <c r="F426" s="3"/>
+      <c r="G426" s="3"/>
+      <c r="H426" s="3"/>
+      <c r="I426" s="3"/>
+      <c r="J426" s="3"/>
+      <c r="K426" s="3"/>
+      <c r="L426" s="3"/>
+      <c r="M426" s="3"/>
+      <c r="N426" s="3"/>
+      <c r="O426" s="3"/>
+      <c r="P426" s="3"/>
+      <c r="Q426" s="3"/>
+      <c r="R426" s="3"/>
+      <c r="S426" s="3"/>
+      <c r="T426" s="3"/>
+      <c r="U426" s="3"/>
+      <c r="V426" s="3"/>
+      <c r="W426" s="3"/>
+      <c r="X426" s="3"/>
+      <c r="Y426" s="3"/>
+      <c r="Z426" s="3"/>
+      <c r="AA426" s="3"/>
+      <c r="AB426" s="3"/>
+      <c r="AC426" s="3"/>
+      <c r="AD426" s="3"/>
+      <c r="AE426" s="3"/>
+      <c r="AF426" s="3"/>
+      <c r="AG426" s="3"/>
+      <c r="AH426" s="3"/>
+      <c r="AI426" s="3"/>
+      <c r="AJ426" s="3"/>
+      <c r="AK426" s="3"/>
+      <c r="AL426" s="3"/>
+      <c r="AM426" s="3"/>
+      <c r="AN426" s="3"/>
+      <c r="AO426" s="3"/>
+    </row>
+    <row r="427" spans="1:41">
+      <c r="A427" s="3"/>
+      <c r="B427" s="3"/>
+      <c r="C427" s="3"/>
+      <c r="D427" s="3"/>
+      <c r="E427" s="3"/>
+      <c r="F427" s="3"/>
+      <c r="G427" s="3"/>
+      <c r="H427" s="3"/>
+      <c r="I427" s="3"/>
+      <c r="J427" s="3"/>
+      <c r="K427" s="3"/>
+      <c r="L427" s="3"/>
+      <c r="M427" s="3"/>
+      <c r="N427" s="3"/>
+      <c r="O427" s="3"/>
+      <c r="P427" s="3"/>
+      <c r="Q427" s="3"/>
+      <c r="R427" s="3"/>
+      <c r="S427" s="3"/>
+      <c r="T427" s="3"/>
+      <c r="U427" s="3"/>
+      <c r="V427" s="3"/>
+      <c r="W427" s="3"/>
+      <c r="X427" s="3"/>
+      <c r="Y427" s="3"/>
+      <c r="Z427" s="3"/>
+      <c r="AA427" s="3"/>
+      <c r="AB427" s="3"/>
+      <c r="AC427" s="3"/>
+      <c r="AD427" s="3"/>
+      <c r="AE427" s="3"/>
+      <c r="AF427" s="3"/>
+      <c r="AG427" s="3"/>
+      <c r="AH427" s="3"/>
+      <c r="AI427" s="3"/>
+      <c r="AJ427" s="3"/>
+      <c r="AK427" s="3"/>
+      <c r="AL427" s="3"/>
+      <c r="AM427" s="3"/>
+      <c r="AN427" s="3"/>
+      <c r="AO427" s="3"/>
+    </row>
+    <row r="428" spans="1:41">
+      <c r="A428" s="3"/>
+      <c r="B428" s="3"/>
+      <c r="C428" s="3"/>
+      <c r="D428" s="3"/>
+      <c r="E428" s="3"/>
+      <c r="F428" s="3"/>
+      <c r="G428" s="3"/>
+      <c r="H428" s="3"/>
+      <c r="I428" s="3"/>
+      <c r="J428" s="3"/>
+      <c r="K428" s="3"/>
+      <c r="L428" s="3"/>
+      <c r="M428" s="3"/>
+      <c r="N428" s="3"/>
+      <c r="O428" s="3"/>
+      <c r="P428" s="3"/>
+      <c r="Q428" s="3"/>
+      <c r="R428" s="3"/>
+      <c r="S428" s="3"/>
+      <c r="T428" s="3"/>
+      <c r="U428" s="3"/>
+      <c r="V428" s="3"/>
+      <c r="W428" s="3"/>
+      <c r="X428" s="3"/>
+      <c r="Y428" s="3"/>
+      <c r="Z428" s="3"/>
+      <c r="AA428" s="3"/>
+      <c r="AB428" s="3"/>
+      <c r="AC428" s="3"/>
+      <c r="AD428" s="3"/>
+      <c r="AE428" s="3"/>
+      <c r="AF428" s="3"/>
+      <c r="AG428" s="3"/>
+      <c r="AH428" s="3"/>
+      <c r="AI428" s="3"/>
+      <c r="AJ428" s="3"/>
+      <c r="AK428" s="3"/>
+      <c r="AL428" s="3"/>
+      <c r="AM428" s="3"/>
+      <c r="AN428" s="3"/>
+      <c r="AO428" s="3"/>
+    </row>
+    <row r="429" spans="1:41">
+      <c r="A429" s="3"/>
+      <c r="B429" s="3"/>
+      <c r="C429" s="3"/>
+      <c r="D429" s="3"/>
+      <c r="E429" s="3"/>
+      <c r="F429" s="3"/>
+      <c r="G429" s="3"/>
+      <c r="H429" s="3"/>
+      <c r="I429" s="3"/>
+      <c r="J429" s="3"/>
+      <c r="K429" s="3"/>
+      <c r="L429" s="3"/>
+      <c r="M429" s="3"/>
+      <c r="N429" s="3"/>
+      <c r="O429" s="3"/>
+      <c r="P429" s="3"/>
+      <c r="Q429" s="3"/>
+      <c r="R429" s="3"/>
+      <c r="S429" s="3"/>
+      <c r="T429" s="3"/>
+      <c r="U429" s="3"/>
+      <c r="V429" s="3"/>
+      <c r="W429" s="3"/>
+      <c r="X429" s="3"/>
+      <c r="Y429" s="3"/>
+      <c r="Z429" s="3"/>
+      <c r="AA429" s="3"/>
+      <c r="AB429" s="3"/>
+      <c r="AC429" s="3"/>
+      <c r="AD429" s="3"/>
+      <c r="AE429" s="3"/>
+      <c r="AF429" s="3"/>
+      <c r="AG429" s="3"/>
+      <c r="AH429" s="3"/>
+      <c r="AI429" s="3"/>
+      <c r="AJ429" s="3"/>
+      <c r="AK429" s="3"/>
+      <c r="AL429" s="3"/>
+      <c r="AM429" s="3"/>
+      <c r="AN429" s="3"/>
+      <c r="AO429" s="3"/>
+    </row>
+    <row r="430" spans="1:41">
+      <c r="A430" s="3"/>
+      <c r="B430" s="3"/>
+      <c r="C430" s="3"/>
+      <c r="D430" s="3"/>
+      <c r="E430" s="3"/>
+      <c r="F430" s="3"/>
+      <c r="G430" s="3"/>
+      <c r="H430" s="3"/>
+      <c r="I430" s="3"/>
+      <c r="J430" s="3"/>
+      <c r="K430" s="3"/>
+      <c r="L430" s="3"/>
+      <c r="M430" s="3"/>
+      <c r="N430" s="3"/>
+      <c r="O430" s="3"/>
+      <c r="P430" s="3"/>
+      <c r="Q430" s="3"/>
+      <c r="R430" s="3"/>
+      <c r="S430" s="3"/>
+      <c r="T430" s="3"/>
+      <c r="U430" s="3"/>
+      <c r="V430" s="3"/>
+      <c r="W430" s="3"/>
+      <c r="X430" s="3"/>
+      <c r="Y430" s="3"/>
+      <c r="Z430" s="3"/>
+      <c r="AA430" s="3"/>
+      <c r="AB430" s="3"/>
+      <c r="AC430" s="3"/>
+      <c r="AD430" s="3"/>
+      <c r="AE430" s="3"/>
+      <c r="AF430" s="3"/>
+      <c r="AG430" s="3"/>
+      <c r="AH430" s="3"/>
+      <c r="AI430" s="3"/>
+      <c r="AJ430" s="3"/>
+      <c r="AK430" s="3"/>
+      <c r="AL430" s="3"/>
+      <c r="AM430" s="3"/>
+      <c r="AN430" s="3"/>
+      <c r="AO430" s="3"/>
+    </row>
+    <row r="431" spans="1:41">
+      <c r="A431" s="3"/>
+      <c r="B431" s="3"/>
+      <c r="C431" s="3"/>
+      <c r="D431" s="3"/>
+      <c r="E431" s="3"/>
+      <c r="F431" s="3"/>
+      <c r="G431" s="3"/>
+      <c r="H431" s="3"/>
+      <c r="I431" s="3"/>
+      <c r="J431" s="3"/>
+      <c r="K431" s="3"/>
+      <c r="L431" s="3"/>
+      <c r="M431" s="3"/>
+      <c r="N431" s="3"/>
+      <c r="O431" s="3"/>
+      <c r="P431" s="3"/>
+      <c r="Q431" s="3"/>
+      <c r="R431" s="3"/>
+      <c r="S431" s="3"/>
+      <c r="T431" s="3"/>
+      <c r="U431" s="3"/>
+      <c r="V431" s="3"/>
+      <c r="W431" s="3"/>
+      <c r="X431" s="3"/>
+      <c r="Y431" s="3"/>
+      <c r="Z431" s="3"/>
+      <c r="AA431" s="3"/>
+      <c r="AB431" s="3"/>
+      <c r="AC431" s="3"/>
+      <c r="AD431" s="3"/>
+      <c r="AE431" s="3"/>
+      <c r="AF431" s="3"/>
+      <c r="AG431" s="3"/>
+      <c r="AH431" s="3"/>
+      <c r="AI431" s="3"/>
+      <c r="AJ431" s="3"/>
+      <c r="AK431" s="3"/>
+      <c r="AL431" s="3"/>
+      <c r="AM431" s="3"/>
+      <c r="AN431" s="3"/>
+      <c r="AO431" s="3"/>
+    </row>
+    <row r="432" spans="1:41">
+      <c r="A432" s="18"/>
+      <c r="B432" s="18"/>
+      <c r="C432" s="18"/>
+      <c r="D432" s="18"/>
+      <c r="E432" s="18"/>
+      <c r="F432" s="18"/>
+      <c r="G432" s="18"/>
+      <c r="H432" s="18"/>
+      <c r="I432" s="18"/>
+      <c r="J432" s="18"/>
+      <c r="K432" s="18"/>
+      <c r="L432" s="18"/>
+      <c r="M432" s="18"/>
+      <c r="N432" s="18"/>
+      <c r="O432" s="18"/>
+      <c r="P432" s="18"/>
+      <c r="Q432" s="18"/>
+      <c r="R432" s="18"/>
+      <c r="S432" s="18"/>
+      <c r="T432" s="18"/>
+      <c r="U432" s="18"/>
+      <c r="V432" s="18"/>
+      <c r="W432" s="18"/>
+      <c r="X432" s="18"/>
+      <c r="Y432" s="18"/>
+      <c r="Z432" s="18"/>
+      <c r="AA432" s="18"/>
+      <c r="AB432" s="18"/>
+      <c r="AC432" s="18"/>
+      <c r="AD432" s="18"/>
+      <c r="AE432" s="18"/>
+      <c r="AF432" s="18"/>
+      <c r="AG432" s="18"/>
+      <c r="AH432" s="18"/>
+      <c r="AI432" s="18"/>
+      <c r="AJ432" s="18"/>
+      <c r="AK432" s="18"/>
+      <c r="AL432" s="18"/>
+      <c r="AM432" s="18"/>
+      <c r="AN432" s="18"/>
+      <c r="AO432" s="18"/>
+    </row>
+    <row r="433" spans="1:41">
+      <c r="A433" s="18"/>
+      <c r="B433" s="18"/>
+      <c r="C433" s="18"/>
+      <c r="D433" s="18"/>
+      <c r="E433" s="18"/>
+      <c r="F433" s="18"/>
+      <c r="G433" s="18"/>
+      <c r="H433" s="18"/>
+      <c r="I433" s="18"/>
+      <c r="J433" s="18"/>
+      <c r="K433" s="18"/>
+      <c r="L433" s="18"/>
+      <c r="M433" s="18"/>
+      <c r="N433" s="18"/>
+      <c r="O433" s="18"/>
+      <c r="P433" s="18"/>
+      <c r="Q433" s="18"/>
+      <c r="R433" s="18"/>
+      <c r="S433" s="18"/>
+      <c r="T433" s="18"/>
+      <c r="U433" s="18"/>
+      <c r="V433" s="18"/>
+      <c r="W433" s="18"/>
+      <c r="X433" s="18"/>
+      <c r="Y433" s="18"/>
+      <c r="Z433" s="18"/>
+      <c r="AA433" s="18"/>
+      <c r="AB433" s="18"/>
+      <c r="AC433" s="18"/>
+      <c r="AD433" s="18"/>
+      <c r="AE433" s="18"/>
+      <c r="AF433" s="18"/>
+      <c r="AG433" s="18"/>
+      <c r="AH433" s="18"/>
+      <c r="AI433" s="18"/>
+      <c r="AJ433" s="18"/>
+      <c r="AK433" s="18"/>
+      <c r="AL433" s="18"/>
+      <c r="AM433" s="18"/>
+      <c r="AN433" s="18"/>
+      <c r="AO433" s="18"/>
+    </row>
+    <row r="434" spans="1:41">
+      <c r="A434" s="18"/>
+      <c r="B434" s="18"/>
+      <c r="C434" s="18"/>
+      <c r="D434" s="18"/>
+      <c r="E434" s="18"/>
+      <c r="F434" s="18"/>
+      <c r="G434" s="18"/>
+      <c r="H434" s="18"/>
+      <c r="I434" s="18"/>
+      <c r="J434" s="18"/>
+      <c r="K434" s="18"/>
+      <c r="L434" s="18"/>
+      <c r="M434" s="18"/>
+      <c r="N434" s="18"/>
+      <c r="O434" s="18"/>
+      <c r="P434" s="18"/>
+      <c r="Q434" s="18"/>
+      <c r="R434" s="18"/>
+      <c r="S434" s="18"/>
+      <c r="T434" s="18"/>
+      <c r="U434" s="18"/>
+      <c r="V434" s="18"/>
+      <c r="W434" s="18"/>
+      <c r="X434" s="18"/>
+      <c r="Y434" s="18"/>
+      <c r="Z434" s="18"/>
+      <c r="AA434" s="18"/>
+      <c r="AB434" s="18"/>
+      <c r="AC434" s="18"/>
+      <c r="AD434" s="18"/>
+      <c r="AE434" s="18"/>
+      <c r="AF434" s="18"/>
+      <c r="AG434" s="18"/>
+      <c r="AH434" s="18"/>
+      <c r="AI434" s="18"/>
+      <c r="AJ434" s="18"/>
+      <c r="AK434" s="18"/>
+      <c r="AL434" s="18"/>
+      <c r="AM434" s="18"/>
+      <c r="AN434" s="18"/>
+      <c r="AO434" s="18"/>
+    </row>
+    <row r="435" spans="1:41">
+      <c r="A435" s="18"/>
+      <c r="B435" s="18"/>
+      <c r="C435" s="18"/>
+      <c r="D435" s="18"/>
+      <c r="E435" s="18"/>
+      <c r="F435" s="18"/>
+      <c r="G435" s="18"/>
+      <c r="H435" s="18"/>
+      <c r="I435" s="18"/>
+      <c r="J435" s="18"/>
+      <c r="K435" s="18"/>
+      <c r="L435" s="18"/>
+      <c r="M435" s="18"/>
+      <c r="N435" s="18"/>
+      <c r="O435" s="18"/>
+      <c r="P435" s="18"/>
+      <c r="Q435" s="18"/>
+      <c r="R435" s="18"/>
+      <c r="S435" s="18"/>
+      <c r="T435" s="18"/>
+      <c r="U435" s="18"/>
+      <c r="V435" s="18"/>
+      <c r="W435" s="18"/>
+      <c r="X435" s="18"/>
+      <c r="Y435" s="18"/>
+      <c r="Z435" s="18"/>
+      <c r="AA435" s="18"/>
+      <c r="AB435" s="18"/>
+      <c r="AC435" s="18"/>
+      <c r="AD435" s="18"/>
+      <c r="AE435" s="18"/>
+      <c r="AF435" s="18"/>
+      <c r="AG435" s="18"/>
+      <c r="AH435" s="18"/>
+      <c r="AI435" s="18"/>
+      <c r="AJ435" s="18"/>
+      <c r="AK435" s="18"/>
+      <c r="AL435" s="18"/>
+      <c r="AM435" s="18"/>
+      <c r="AN435" s="18"/>
+      <c r="AO435" s="18"/>
+    </row>
+    <row r="436" spans="1:41">
+      <c r="A436" s="18"/>
+      <c r="B436" s="18"/>
+      <c r="C436" s="18"/>
+      <c r="D436" s="18"/>
+      <c r="E436" s="18"/>
+      <c r="F436" s="18"/>
+      <c r="G436" s="18"/>
+      <c r="H436" s="18"/>
+      <c r="I436" s="18"/>
+      <c r="J436" s="18"/>
+      <c r="K436" s="18"/>
+      <c r="L436" s="18"/>
+      <c r="M436" s="18"/>
+      <c r="N436" s="18"/>
+      <c r="O436" s="18"/>
+      <c r="P436" s="18"/>
+      <c r="Q436" s="18"/>
+      <c r="R436" s="18"/>
+      <c r="S436" s="18"/>
+      <c r="T436" s="18"/>
+      <c r="U436" s="18"/>
+      <c r="V436" s="18"/>
+      <c r="W436" s="18"/>
+      <c r="X436" s="18"/>
+      <c r="Y436" s="18"/>
+      <c r="Z436" s="18"/>
+      <c r="AA436" s="18"/>
+      <c r="AB436" s="18"/>
+      <c r="AC436" s="18"/>
+      <c r="AD436" s="18"/>
+      <c r="AE436" s="18"/>
+      <c r="AF436" s="18"/>
+      <c r="AG436" s="18"/>
+      <c r="AH436" s="18"/>
+      <c r="AI436" s="18"/>
+      <c r="AJ436" s="18"/>
+      <c r="AK436" s="18"/>
+      <c r="AL436" s="18"/>
+      <c r="AM436" s="18"/>
+      <c r="AN436" s="18"/>
+      <c r="AO436" s="18"/>
+    </row>
+    <row r="437" spans="1:41">
+      <c r="A437" s="18"/>
+      <c r="B437" s="18"/>
+      <c r="C437" s="18"/>
+      <c r="D437" s="18"/>
+      <c r="E437" s="18"/>
+      <c r="F437" s="18"/>
+      <c r="G437" s="18"/>
+      <c r="H437" s="18"/>
+      <c r="I437" s="18"/>
+      <c r="J437" s="18"/>
+      <c r="K437" s="18"/>
+      <c r="L437" s="18"/>
+      <c r="M437" s="18"/>
+      <c r="N437" s="18"/>
+      <c r="O437" s="18"/>
+      <c r="P437" s="18"/>
+      <c r="Q437" s="18"/>
+      <c r="R437" s="18"/>
+      <c r="S437" s="18"/>
+      <c r="T437" s="18"/>
+      <c r="U437" s="18"/>
+      <c r="V437" s="18"/>
+      <c r="W437" s="18"/>
+      <c r="X437" s="18"/>
+      <c r="Y437" s="18"/>
+      <c r="Z437" s="18"/>
+      <c r="AA437" s="18"/>
+      <c r="AB437" s="18"/>
+      <c r="AC437" s="18"/>
+      <c r="AD437" s="18"/>
+      <c r="AE437" s="18"/>
+      <c r="AF437" s="18"/>
+      <c r="AG437" s="18"/>
+      <c r="AH437" s="18"/>
+      <c r="AI437" s="18"/>
+      <c r="AJ437" s="18"/>
+      <c r="AK437" s="18"/>
+      <c r="AL437" s="18"/>
+      <c r="AM437" s="18"/>
+      <c r="AN437" s="18"/>
+      <c r="AO437" s="18"/>
+    </row>
+    <row r="438" spans="1:41">
+      <c r="A438" s="18"/>
+      <c r="B438" s="18"/>
+      <c r="C438" s="18"/>
+      <c r="D438" s="18"/>
+      <c r="E438" s="18"/>
+      <c r="F438" s="18"/>
+      <c r="G438" s="18"/>
+      <c r="H438" s="18"/>
+      <c r="I438" s="18"/>
+      <c r="J438" s="18"/>
+      <c r="K438" s="18"/>
+      <c r="L438" s="18"/>
+      <c r="M438" s="18"/>
+      <c r="N438" s="18"/>
+      <c r="O438" s="18"/>
+      <c r="P438" s="18"/>
+      <c r="Q438" s="18"/>
+      <c r="R438" s="18"/>
+      <c r="S438" s="18"/>
+      <c r="T438" s="18"/>
+      <c r="U438" s="18"/>
+      <c r="V438" s="18"/>
+      <c r="W438" s="18"/>
+      <c r="X438" s="18"/>
+      <c r="Y438" s="18"/>
+      <c r="Z438" s="18"/>
+      <c r="AA438" s="18"/>
+      <c r="AB438" s="18"/>
+      <c r="AC438" s="18"/>
+      <c r="AD438" s="18"/>
+      <c r="AE438" s="18"/>
+      <c r="AF438" s="18"/>
+      <c r="AG438" s="18"/>
+      <c r="AH438" s="18"/>
+      <c r="AI438" s="18"/>
+      <c r="AJ438" s="18"/>
+      <c r="AK438" s="18"/>
+      <c r="AL438" s="18"/>
+      <c r="AM438" s="18"/>
+      <c r="AN438" s="18"/>
+      <c r="AO438" s="18"/>
+    </row>
+    <row r="439" spans="1:41">
+      <c r="A439" s="18"/>
+      <c r="B439" s="18"/>
+      <c r="C439" s="18"/>
+      <c r="D439" s="18"/>
+      <c r="E439" s="18"/>
+      <c r="F439" s="18"/>
+      <c r="G439" s="18"/>
+      <c r="H439" s="18"/>
+      <c r="I439" s="18"/>
+      <c r="J439" s="18"/>
+      <c r="K439" s="18"/>
+      <c r="L439" s="18"/>
+      <c r="M439" s="18"/>
+      <c r="N439" s="18"/>
+      <c r="O439" s="18"/>
+      <c r="P439" s="18"/>
+      <c r="Q439" s="18"/>
+      <c r="R439" s="18"/>
+      <c r="S439" s="18"/>
+      <c r="T439" s="18"/>
+      <c r="U439" s="18"/>
+      <c r="V439" s="18"/>
+      <c r="W439" s="18"/>
+      <c r="X439" s="18"/>
+      <c r="Y439" s="18"/>
+      <c r="Z439" s="18"/>
+      <c r="AA439" s="18"/>
+      <c r="AB439" s="18"/>
+      <c r="AC439" s="18"/>
+      <c r="AD439" s="18"/>
+      <c r="AE439" s="18"/>
+      <c r="AF439" s="18"/>
+      <c r="AG439" s="18"/>
+      <c r="AH439" s="18"/>
+      <c r="AI439" s="18"/>
+      <c r="AJ439" s="18"/>
+      <c r="AK439" s="18"/>
+      <c r="AL439" s="18"/>
+      <c r="AM439" s="18"/>
+      <c r="AN439" s="18"/>
+      <c r="AO439" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="7">
+    <mergeCell ref="C339:C340"/>
+    <mergeCell ref="C390:C392"/>
+    <mergeCell ref="D339:D340"/>
+    <mergeCell ref="D390:D392"/>
+    <mergeCell ref="E339:E340"/>
+    <mergeCell ref="E390:E392"/>
     <mergeCell ref="A1:B4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
